--- a/build/assets/Audio/audio_manifest.xlsx
+++ b/build/assets/Audio/audio_manifest.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,6 +43,11 @@
     <font>
       <name val="Arial"/>
       <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -85,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -94,6 +99,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -459,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -535,6 +542,55 @@
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Filenames must match EXACTLY (lowercase, underscores). Hindi column uses Nirmala UI (Devanagari).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>AUDIO FORMAT - please deliver exactly this:</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WAV, 16-bit PCM, MONO, 48 kHz.  One file per row, named as column C (e.g. vo_landing.wav).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    16-bit WAV is a hard requirement, not a preference: the word-by-word highlighting is timed by</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    reading the waveform, and that reader only understands 16-bit PCM WAV. An MP3/OGG/M4A delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    still plays, but the highlighting silently falls back to guessed timing and drifts out of sync.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    No added silence, no fades, no music bed, no normalisation to a brickwall - a clean room take.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Send the folder as-is; the build renames and encodes (Opus 28k mono) on its own.</t>
         </is>
       </c>
     </row>
@@ -609,7 +665,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>vo_landing.ogg</t>
+          <t>vo_landing.wav</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -642,7 +698,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>vo_g1_correct.ogg</t>
+          <t>vo_g1_correct.wav</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -675,7 +731,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>vo_g1_correct2.ogg</t>
+          <t>vo_g1_correct2.wav</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -708,7 +764,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>vo_g1_hint.ogg</t>
+          <t>vo_g1_hint.wav</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -741,7 +797,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>vo_g1_hint2.ogg</t>
+          <t>vo_g1_hint2.wav</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -774,7 +830,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>vo_g1_next.ogg</t>
+          <t>vo_g1_next.wav</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -807,7 +863,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>vo_g1_prompt.ogg</t>
+          <t>vo_g1_prompt.wav</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -840,7 +896,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>vo_g2_done.ogg</t>
+          <t>vo_g2_done.wav</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -873,7 +929,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>vo_g2_hint.ogg</t>
+          <t>vo_g2_hint.wav</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -906,7 +962,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>vo_g2_more.ogg</t>
+          <t>vo_g2_more.wav</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -939,7 +995,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>vo_g2_prompt.ogg</t>
+          <t>vo_g2_prompt.wav</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -972,7 +1028,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>vo_g2_reveal.ogg</t>
+          <t>vo_g2_reveal.wav</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1005,7 +1061,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>vo_g2_try.ogg</t>
+          <t>vo_g2_try.wav</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1038,7 +1094,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>vo_g3_correct.ogg</t>
+          <t>vo_g3_correct.wav</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1071,7 +1127,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>vo_g3_prompt.ogg</t>
+          <t>vo_g3_prompt.wav</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1104,7 +1160,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>vo_g3_reveal.ogg</t>
+          <t>vo_g3_reveal.wav</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1137,7 +1193,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>vo_g3_try.ogg</t>
+          <t>vo_g3_try.wav</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -1170,7 +1226,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>vo_g5_correct.ogg</t>
+          <t>vo_g5_correct.wav</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1203,7 +1259,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>vo_g5_hint.ogg</t>
+          <t>vo_g5_hint.wav</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1236,7 +1292,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>vo_g5_prompt.ogg</t>
+          <t>vo_g5_prompt.wav</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -1269,7 +1325,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>vo_g5_show.ogg</t>
+          <t>vo_g5_show.wav</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1302,7 +1358,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>vo_g5_try.ogg</t>
+          <t>vo_g5_try.wav</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -1335,7 +1391,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>vo_line_l1.ogg</t>
+          <t>vo_line_l1.wav</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1368,7 +1424,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>vo_line_l2.ogg</t>
+          <t>vo_line_l2.wav</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -1401,7 +1457,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>vo_line_l3.ogg</t>
+          <t>vo_line_l3.wav</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -1434,7 +1490,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>vo_line_l6.ogg</t>
+          <t>vo_line_l6.wav</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -1467,7 +1523,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_ch.ogg</t>
+          <t>vo_ltr_ch.wav</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -1500,7 +1556,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_l.ogg</t>
+          <t>vo_ltr_l.wav</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -1533,7 +1589,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_m.ogg</t>
+          <t>vo_ltr_m.wav</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -1566,7 +1622,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_n.ogg</t>
+          <t>vo_ltr_n.wav</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -1599,7 +1655,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_p.ogg</t>
+          <t>vo_ltr_p.wav</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -1632,7 +1688,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_r.ogg</t>
+          <t>vo_ltr_r.wav</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -1665,7 +1721,7 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_done.ogg</t>
+          <t>vo_p1_done.wav</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -1698,7 +1754,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_hint.ogg</t>
+          <t>vo_p1_hint.wav</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -1731,7 +1787,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_more.ogg</t>
+          <t>vo_p1_more.wav</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -1764,7 +1820,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_prompt.ogg</t>
+          <t>vo_p1_prompt.wav</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -1797,7 +1853,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_reveal.ogg</t>
+          <t>vo_p1_reveal.wav</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -1830,7 +1886,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_try.ogg</t>
+          <t>vo_p1_try.wav</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -1863,7 +1919,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_correct.ogg</t>
+          <t>vo_p4_correct.wav</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -1896,7 +1952,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_prompt.ogg</t>
+          <t>vo_p4_prompt.wav</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -1929,7 +1985,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_reveal.ogg</t>
+          <t>vo_p4_reveal.wav</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -1962,7 +2018,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_try.ogg</t>
+          <t>vo_p4_try.wav</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -1995,7 +2051,7 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_done.ogg</t>
+          <t>vo_p7_done.wav</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -2028,7 +2084,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_hint.ogg</t>
+          <t>vo_p7_hint.wav</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -2061,7 +2117,7 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_more.ogg</t>
+          <t>vo_p7_more.wav</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -2094,7 +2150,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_prompt.ogg</t>
+          <t>vo_p7_prompt.wav</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -2127,7 +2183,7 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_reveal.ogg</t>
+          <t>vo_p7_reveal.wav</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -2160,7 +2216,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_try.ogg</t>
+          <t>vo_p7_try.wav</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -2193,7 +2249,7 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>vo_p8_prompt.ogg</t>
+          <t>vo_p8_prompt.wav</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -2226,7 +2282,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>vo_snd_ch.ogg</t>
+          <t>vo_snd_ch.wav</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -2259,7 +2315,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>vo_snd_m.ogg</t>
+          <t>vo_snd_m.wav</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -2292,7 +2348,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>vo_snd_p.ogg</t>
+          <t>vo_snd_p.wav</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -2325,7 +2381,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>vo_t1_explain.ogg</t>
+          <t>vo_t1_explain.wav</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -2358,7 +2414,7 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>vo_t2_prompt.ogg</t>
+          <t>vo_t2_prompt.wav</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -2391,7 +2447,7 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>vo_t3_explain.ogg</t>
+          <t>vo_t3_explain.wav</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -2424,7 +2480,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>vo_t4_prompt.ogg</t>
+          <t>vo_t4_prompt.wav</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -2457,7 +2513,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>vo_t5_explain.ogg</t>
+          <t>vo_t5_explain.wav</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -2490,7 +2546,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>vo_t6_prompt.ogg</t>
+          <t>vo_t6_prompt.wav</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -2523,7 +2579,7 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>vo_w_aam.ogg</t>
+          <t>vo_w_aam.wav</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -2556,7 +2612,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chammach.ogg</t>
+          <t>vo_w_chammach.wav</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -2589,7 +2645,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chand.ogg</t>
+          <t>vo_w_chand.wav</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -2622,7 +2678,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chashma.ogg</t>
+          <t>vo_w_chashma.wav</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -2655,7 +2711,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chidiya.ogg</t>
+          <t>vo_w_chidiya.wav</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -2688,7 +2744,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chinti.ogg</t>
+          <t>vo_w_chinti.wav</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -2721,7 +2777,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chuha.ogg</t>
+          <t>vo_w_chuha.wav</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -2754,7 +2810,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>vo_w_ghar.ogg</t>
+          <t>vo_w_ghar.wav</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -2787,7 +2843,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kabutar.ogg</t>
+          <t>vo_w_kabutar.wav</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -2820,7 +2876,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kamal.ogg</t>
+          <t>vo_w_kamal.wav</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -2853,7 +2909,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kauaa.ogg</t>
+          <t>vo_w_kauaa.wav</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -2886,7 +2942,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kela.ogg</t>
+          <t>vo_w_kela.wav</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -2919,7 +2975,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>vo_w_laal.ogg</t>
+          <t>vo_w_laal.wav</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -2952,7 +3008,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>vo_w_laddu.ogg</t>
+          <t>vo_w_laddu.wav</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -2985,7 +3041,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>vo_w_machhli.ogg</t>
+          <t>vo_w_machhli.wav</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -3018,7 +3074,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>vo_w_mala.ogg</t>
+          <t>vo_w_mala.wav</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -3051,7 +3107,7 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>vo_w_mama.ogg</t>
+          <t>vo_w_mama.wav</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -3084,7 +3140,7 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>vo_w_muli.ogg</t>
+          <t>vo_w_muli.wav</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -3117,7 +3173,7 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>vo_w_pani.ogg</t>
+          <t>vo_w_pani.wav</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -3150,7 +3206,7 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>vo_w_papita.ogg</t>
+          <t>vo_w_papita.wav</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -3183,7 +3239,7 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>vo_w_patang.ogg</t>
+          <t>vo_w_patang.wav</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -3216,7 +3272,7 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>vo_w_patta.ogg</t>
+          <t>vo_w_patta.wav</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -3249,7 +3305,7 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>vo_w_payal.ogg</t>
+          <t>vo_w_payal.wav</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">

--- a/build/assets/Audio/audio_manifest.xlsx
+++ b/build/assets/Audio/audio_manifest.xlsx
@@ -1000,7 +1000,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>जिन शब्दों में “प” की आवाज़ सुनाई दे, उन पर टैप कीजिए।</t>
+          <t>“प” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>page 9 · correct; page 10 · correct</t>
+          <t>page 12 · correct; page 13 · correct</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>page 10 · hint</t>
+          <t>page 13 · hint</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>page 10 · prompt</t>
+          <t>page 13 · prompt</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>page 9 · prompt</t>
+          <t>page 12 · prompt</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>page 10 · try_again</t>
+          <t>page 13 · try_again</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>page 12 · whole line</t>
+          <t>page 9 · whole line</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>page 8 · option ल; page 12 · option ल</t>
+          <t>page 8 · option ल; page 9 · option ल</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>page 3 · target; page 3 · option म; page 12 · option म</t>
+          <t>page 3 · target; page 3 · option म; page 9 · option म</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>page 12 · target; page 12 · option न</t>
+          <t>page 9 · target; page 9 · option न</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>page 11 · done</t>
+          <t>page 10 · done</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>page 11 · hint</t>
+          <t>page 10 · hint</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>page 11 · more</t>
+          <t>page 10 · more</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>जिन शब्दों में “म” की आवाज़ सुनाई दे, उन पर टैप कीजिए।</t>
+          <t>“म” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>page 11 · prompt</t>
+          <t>page 10 · prompt</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="G37" s="4" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>page 11 · reveal</t>
+          <t>page 10 · reveal</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>page 11 · try_again</t>
+          <t>page 10 · try_again</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>page 12 · correct</t>
+          <t>page 9 · correct</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>page 12 · prompt</t>
+          <t>page 9 · prompt</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>page 12 · reveal</t>
+          <t>page 9 · reveal</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>page 12 · try_again</t>
+          <t>page 9 · try_again</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>page 13 · done</t>
+          <t>page 11 · done</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>page 13 · hint</t>
+          <t>page 11 · hint</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>page 13 · more</t>
+          <t>page 11 · more</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>जिन शब्दों में “च” की आवाज़ सुनाई दे, उन पर टैप कीजिए।</t>
+          <t>“च” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>page 13 · prompt</t>
+          <t>page 11 · prompt</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="G47" s="4" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>page 13 · reveal</t>
+          <t>page 11 · reveal</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>page 13 · try_again</t>
+          <t>page 11 · try_again</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>page 2 · sound; page 13 · target</t>
+          <t>page 2 · sound; page 11 · target</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>page 4 · sound; page 11 · target</t>
+          <t>page 4 · sound; page 10 · target</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>page 6 · sound; page 7 · target; page 9 · target; page 10 · target (+1 more)</t>
+          <t>page 6 · sound; page 7 · target; page 12 · target; page 13 · target (+1 more)</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>page 5 · teach step 5</t>
+          <t>page 5 · teach step 4</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>page 1 · teach step 5</t>
+          <t>page 1 · teach step 4</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>page 3 · teach step 5</t>
+          <t>page 3 · teach step 4</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>page 10 · picture चम्मच; page 14 · round 2 balloon चम्मच</t>
+          <t>page 13 · picture चम्मच; page 14 · round 2 balloon चम्मच</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>page 9 · picture चाँद; page 13 · picture चाँद; page 14 · round 2 balloon चाँद</t>
+          <t>page 11 · picture चाँद; page 12 · picture चाँद; page 14 · round 2 balloon चाँद</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>page 13 · picture चश्मा</t>
+          <t>page 11 · picture चश्मा</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>page 11 · picture चिड़िया</t>
+          <t>page 10 · picture चिड़िया</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>page 2 · word_name; page 10 · picture चूहा; page 14 · round 2 balloon चूहा</t>
+          <t>page 2 · word_name; page 13 · picture चूहा; page 14 · round 2 balloon चूहा</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>page 13 · picture लाल; page 14 · round 1 refill लाल</t>
+          <t>page 11 · picture लाल; page 14 · round 1 refill लाल</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>page 11 · picture लड्डू</t>
+          <t>page 10 · picture लड्डू</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>page 13 · picture माला; page 14 · round 1 refill माला</t>
+          <t>page 11 · picture माला; page 14 · round 1 refill माला</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>page 11 · picture मामा</t>
+          <t>page 10 · picture मामा</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>page 4 · word_name; page 11 · picture मूली; page 14 · round 1 refill मूली</t>
+          <t>page 4 · word_name; page 10 · picture मूली; page 14 · round 1 refill मूली</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>page 10 · picture पानी; page 14 · round 1 balloon पानी</t>
+          <t>page 13 · picture पानी; page 14 · round 1 balloon पानी</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>page 7 · picture पतंग; page 9 · picture पतंग; page 14 · round 1 balloon पतंग</t>
+          <t>page 7 · picture पतंग; page 12 · picture पतंग; page 14 · round 1 balloon पतंग</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>page 10 · picture पायल</t>
+          <t>page 13 · picture पायल</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">

--- a/build/assets/Audio/audio_manifest.xlsx
+++ b/build/assets/Audio/audio_manifest.xlsx
@@ -1104,7 +1104,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>page 8 · correct</t>
+          <t>page 10 · correct</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>page 8 · prompt</t>
+          <t>page 10 · prompt</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>page 8 · reveal</t>
+          <t>page 10 · reveal</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>page 8 · try_again</t>
+          <t>page 10 · try_again</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>page 1 · prompt; page 1 · whole line; page 8 · whole line</t>
+          <t>page 1 · prompt; page 1 · whole line; page 10 · whole line</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>page 9 · whole line</t>
+          <t>page 11 · whole line</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>page 1 · target; page 1 · option च; page 8 · target; page 8 · option च</t>
+          <t>page 1 · target; page 1 · option च; page 10 · target; page 10 · option च</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>page 8 · option ल; page 9 · option ल</t>
+          <t>page 10 · option ल; page 11 · option ल</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>page 3 · target; page 3 · option म; page 9 · option म</t>
+          <t>page 3 · target; page 3 · option म; page 11 · option म</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>page 9 · target; page 9 · option न</t>
+          <t>page 11 · target; page 11 · option न</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>page 8 · option र</t>
+          <t>page 10 · option र</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>page 10 · done</t>
+          <t>page 8 · done</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>page 10 · hint</t>
+          <t>page 8 · hint</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>page 10 · more</t>
+          <t>page 8 · more</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>page 10 · prompt</t>
+          <t>page 8 · prompt</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>page 10 · reveal</t>
+          <t>page 8 · reveal</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>page 10 · try_again</t>
+          <t>page 8 · try_again</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>page 9 · correct</t>
+          <t>page 11 · correct</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>page 9 · prompt</t>
+          <t>page 11 · prompt</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>page 9 · reveal</t>
+          <t>page 11 · reveal</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>page 9 · try_again</t>
+          <t>page 11 · try_again</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>page 11 · done</t>
+          <t>page 9 · done</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>page 11 · hint</t>
+          <t>page 9 · hint</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>page 11 · more</t>
+          <t>page 9 · more</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>page 11 · prompt</t>
+          <t>page 9 · prompt</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>page 11 · reveal</t>
+          <t>page 9 · reveal</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>page 11 · try_again</t>
+          <t>page 9 · try_again</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>page 2 · sound; page 11 · target</t>
+          <t>page 2 · sound; page 9 · target</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>page 4 · sound; page 10 · target</t>
+          <t>page 4 · sound; page 8 · target</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>page 11 · picture चाँद; page 12 · picture चाँद; page 14 · round 2 balloon चाँद</t>
+          <t>page 9 · picture चाँद; page 12 · picture चाँद; page 14 · round 2 balloon चाँद</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>page 11 · picture चश्मा</t>
+          <t>page 9 · picture चश्मा</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>page 10 · picture चिड़िया</t>
+          <t>page 8 · picture चिड़िया</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>page 11 · picture लाल; page 14 · round 1 refill लाल</t>
+          <t>page 9 · picture लाल; page 14 · round 1 refill लाल</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>page 10 · picture लड्डू</t>
+          <t>page 8 · picture लड्डू</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>page 11 · picture माला; page 14 · round 1 refill माला</t>
+          <t>page 9 · picture माला; page 14 · round 1 refill माला</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>page 10 · picture मामा</t>
+          <t>page 8 · picture मामा</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>page 4 · word_name; page 10 · picture मूली; page 14 · round 1 refill मूली</t>
+          <t>page 4 · word_name; page 8 · picture मूली; page 14 · round 1 refill मूली</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">

--- a/build/assets/Audio/audio_manifest.xlsx
+++ b/build/assets/Audio/audio_manifest.xlsx
@@ -670,7 +670,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>नमस्ते दोस्त! मैं हूँ Swiftee। आज हम जानेंगे कि वाक्य में कौन-सी ध्वनि बार-बार सुनाई देती है। सुनो—काला कौआ काँव-काँव करता। इस वाक्य में क की ध्वनि यानी आवाज़ बार-बार आ रही है।</t>
+          <t>आज हम जानेंगे वाक्य में बार-बार आने वाली ध्वनि यानी आवाज़ के बारे में।</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -680,11 +680,11 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>RE-RECORD - the line was re-scripted after this take</t>
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>176</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G3" s="4" t="n">
@@ -746,7 +746,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G4" s="4" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G5" s="4" t="n">
@@ -812,7 +812,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G6" s="4" t="n">
@@ -845,7 +845,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G7" s="4" t="n">
@@ -878,7 +878,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G8" s="4" t="n">
@@ -911,7 +911,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G9" s="4" t="n">
@@ -944,7 +944,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
@@ -977,7 +977,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G11" s="4" t="n">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>RE-RECORD - build differs from the delivered take</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G13" s="4" t="n">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G14" s="4" t="n">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G15" s="4" t="n">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G16" s="4" t="n">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G17" s="4" t="n">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G18" s="4" t="n">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G19" s="4" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G20" s="4" t="n">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G21" s="4" t="n">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G22" s="4" t="n">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G23" s="4" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G24" s="4" t="n">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G25" s="4" t="n">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G26" s="4" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G27" s="4" t="n">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
         </is>
       </c>
       <c r="G28" s="4" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
         </is>
       </c>
       <c r="G29" s="4" t="n">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
         </is>
       </c>
       <c r="G30" s="4" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
         </is>
       </c>
       <c r="G31" s="4" t="n">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
         </is>
       </c>
       <c r="G32" s="4" t="n">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
         </is>
       </c>
       <c r="G33" s="4" t="n">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G34" s="4" t="n">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G35" s="4" t="n">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G36" s="4" t="n">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>RE-RECORD - build differs from the delivered take</t>
         </is>
       </c>
       <c r="G37" s="4" t="n">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G38" s="4" t="n">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G39" s="4" t="n">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G40" s="4" t="n">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G41" s="4" t="n">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G42" s="4" t="n">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G43" s="4" t="n">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G44" s="4" t="n">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G45" s="4" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G46" s="4" t="n">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>RE-RECORD - build differs from the delivered take</t>
         </is>
       </c>
       <c r="G47" s="4" t="n">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G48" s="4" t="n">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G49" s="4" t="n">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>RE-RECORD - build differs from the delivered take</t>
         </is>
       </c>
       <c r="G50" s="4" t="n">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
         </is>
       </c>
       <c r="G51" s="4" t="n">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G52" s="4" t="n">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G53" s="4" t="n">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G54" s="4" t="n">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G55" s="4" t="n">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G56" s="4" t="n">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G57" s="4" t="n">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G58" s="4" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G59" s="4" t="n">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G60" s="4" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G61" s="4" t="n">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G62" s="4" t="n">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G63" s="4" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G64" s="4" t="n">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G65" s="4" t="n">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G66" s="4" t="n">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G67" s="4" t="n">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G68" s="4" t="n">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>RE-RECORD - build differs from the delivered take</t>
         </is>
       </c>
       <c r="G69" s="4" t="n">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G70" s="4" t="n">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G71" s="4" t="n">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G72" s="4" t="n">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G73" s="4" t="n">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G74" s="4" t="n">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G75" s="4" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G76" s="4" t="n">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G77" s="4" t="n">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G78" s="4" t="n">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G79" s="4" t="n">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G80" s="4" t="n">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G81" s="4" t="n">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>machine TTS - replace</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G82" s="4" t="n">

--- a/build/assets/Audio/audio_manifest.xlsx
+++ b/build/assets/Audio/audio_manifest.xlsx
@@ -670,7 +670,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>आज हम जानेंगे वाक्य में बार-बार आने वाली ध्वनि यानी आवाज़ के बारे में।</t>
+          <t>नमस्ते दोस्तो! आज हम जानेंगे वाक्य में बार-बार आने वाली ध्वनि यानी आवाज़ के बारे में।</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3">

--- a/build/assets/Audio/audio_manifest.xlsx
+++ b/build/assets/Audio/audio_manifest.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>RE-RECORD - the line was re-scripted after this take</t>
+          <t>RE-RECORD - SME asked for a new line (column D is the line to record)</t>
         </is>
       </c>
       <c r="G2" s="4" t="n">

--- a/build/assets/Audio/audio_manifest.xlsx
+++ b/build/assets/Audio/audio_manifest.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>RE-RECORD - SME asked for a new line (column D is the line to record)</t>
+          <t>SYNTHESISED - record a human take of the line in column D</t>
         </is>
       </c>
       <c r="G2" s="4" t="n">

--- a/build/assets/Audio/audio_manifest.xlsx
+++ b/build/assets/Audio/audio_manifest.xlsx
@@ -708,7 +708,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>page 14 · correct</t>
+          <t>page 13 · correct</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>page 14 · round 2 correct; page 14 · round 2 done</t>
+          <t>page 13 · round 2 correct; page 13 · round 2 done</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>page 14 · hint</t>
+          <t>page 13 · hint</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>page 14 · round 2 hint</t>
+          <t>page 13 · round 2 hint</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>page 14 · round 2 prompt</t>
+          <t>page 13 · round 2 prompt</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>page 14 · prompt</t>
+          <t>page 13 · prompt</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>page 12 · correct; page 13 · correct</t>
+          <t>page 12 · correct; page 12 · correct (2nd half)</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>page 13 · hint</t>
+          <t>page 12 · hint (2nd half)</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>page 13 · prompt</t>
+          <t>page 12 · prompt (2nd half)</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>page 13 · try_again</t>
+          <t>page 12 · try_again (2nd half)</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>page 15 · prompt</t>
+          <t>page 14 · prompt</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>page 6 · sound; page 7 · target; page 12 · target; page 13 · target (+1 more)</t>
+          <t>page 6 · sound; page 7 · target; page 12 · target; page 12 · target (2nd half) (+1 more)</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>page 7 · picture आम; page 14 · round 1 balloon आम; page 14 · round 2 refill आम</t>
+          <t>page 7 · picture आम; page 13 · round 1 balloon आम; page 13 · round 2 refill आम</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>page 13 · picture चम्मच; page 14 · round 2 balloon चम्मच</t>
+          <t>page 12 · picture चम्मच (2nd half); page 13 · round 2 balloon चम्मच</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>page 9 · picture चाँद; page 12 · picture चाँद; page 14 · round 2 balloon चाँद</t>
+          <t>page 9 · picture चाँद; page 12 · picture चाँद; page 13 · round 2 balloon चाँद</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>page 14 · round 2 balloon चींटी</t>
+          <t>page 13 · round 2 balloon चींटी</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>page 2 · word_name; page 13 · picture चूहा; page 14 · round 2 balloon चूहा</t>
+          <t>page 2 · word_name; page 12 · picture चूहा (2nd half); page 13 · round 2 balloon चूहा</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>page 14 · round 1 balloon घर; page 14 · round 2 refill घर</t>
+          <t>page 13 · round 1 balloon घर; page 13 · round 2 refill घर</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>page 14 · round 2 balloon कबूतर</t>
+          <t>page 13 · round 2 balloon कबूतर</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>page 14 · round 2 balloon कमल</t>
+          <t>page 13 · round 2 balloon कमल</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>page 14 · round 2 balloon कौआ</t>
+          <t>page 13 · round 2 balloon कौआ</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>page 7 · picture केला; page 14 · round 1 balloon केला; page 14 · round 2 balloon केला</t>
+          <t>page 7 · picture केला; page 13 · round 1 balloon केला; page 13 · round 2 balloon केला</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>page 9 · picture लाल; page 14 · round 1 refill लाल</t>
+          <t>page 9 · picture लाल; page 13 · round 1 refill लाल</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>page 14 · round 1 balloon मछली; page 14 · round 2 refill मछली</t>
+          <t>page 13 · round 1 balloon मछली; page 13 · round 2 refill मछली</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>page 9 · picture माला; page 14 · round 1 refill माला</t>
+          <t>page 9 · picture माला; page 13 · round 1 refill माला</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>page 4 · word_name; page 8 · picture मूली; page 14 · round 1 refill मूली</t>
+          <t>page 4 · word_name; page 8 · picture मूली; page 13 · round 1 refill मूली</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>page 13 · picture पानी; page 14 · round 1 balloon पानी</t>
+          <t>page 12 · picture पानी (2nd half); page 13 · round 1 balloon पानी</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>page 6 · word_name; page 7 · picture पपीता; page 14 · round 1 balloon पपीता</t>
+          <t>page 6 · word_name; page 7 · picture पपीता; page 13 · round 1 balloon पपीता</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>page 7 · picture पतंग; page 12 · picture पतंग; page 14 · round 1 balloon पतंग</t>
+          <t>page 7 · picture पतंग; page 12 · picture पतंग; page 13 · round 1 balloon पतंग</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>page 14 · round 1 balloon पत्ता</t>
+          <t>page 13 · round 1 balloon पत्ता</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>page 13 · picture पायल</t>
+          <t>page 12 · picture पायल (2nd half)</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">

--- a/build/assets/Audio/audio_manifest.xlsx
+++ b/build/assets/Audio/audio_manifest.xlsx
@@ -51,7 +51,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3B70"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -90,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -99,6 +104,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -515,13 +521,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="D2" t="n">
         <v>81</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -546,49 +552,49 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>AUDIO FORMAT - please deliver exactly this:</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">    WAV, 16-bit PCM, MONO, 48 kHz.  One file per row, named as column C (e.g. vo_landing.wav).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">    16-bit WAV is a hard requirement, not a preference: the word-by-word highlighting is timed by</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">    reading the waveform, and that reader only understands 16-bit PCM WAV. An MP3/OGG/M4A delivery</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">    still plays, but the highlighting silently falls back to guessed timing and drifts out of sync.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">    No added silence, no fades, no music bed, no normalisation to a brickwall - a clean room take.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">    Send the folder as-is; the build renames and encodes (Opus 28k mono) on its own.</t>
         </is>
@@ -605,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -924,31 +930,31 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>vo_g2_hint</t>
+          <t>vo_g2_h1</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>vo_g2_hint.wav</t>
+          <t>vo_g2_h1.wav</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>हर शब्द को ध्यान से देखिए और सुनिए। किस शब्द में प की आवाज़ आ रही है?</t>
+          <t>फिर से सुनिए। जिन शब्दों की शुरुआत ‘प’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>page 7 · hint</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>delivered - do NOT re-record</t>
+          <t>page 7 · h1</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11">
@@ -957,31 +963,31 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>vo_g2_more</t>
+          <t>vo_g2_h2</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>vo_g2_more.wav</t>
+          <t>vo_g2_h2.wav</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>एक और प वाले शब्द पर टैप कीजिए।</t>
+          <t>जिन शब्दों की शुरुआत ‘प’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>page 7 · more</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>delivered - do NOT re-record</t>
+          <t>page 7 · h2</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
         </is>
       </c>
       <c r="G11" s="4" t="n">
-        <v>31</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12">
@@ -990,31 +996,31 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>vo_g2_prompt</t>
+          <t>vo_g2_h3</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>vo_g2_prompt.wav</t>
+          <t>vo_g2_h3.wav</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>“प” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
+          <t>देखिए, ‘पपीता’ और ‘पतंग’ की शुरुआत ‘प’ की आवाज़ से होती है। इन पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>page 7 · prompt</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
+          <t>page 7 · h3</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>38</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
@@ -1023,22 +1029,22 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>vo_g2_reveal</t>
+          <t>vo_g2_hint</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>vo_g2_reveal.wav</t>
+          <t>vo_g2_hint.wav</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>सुनो — इसमें प की आवाज़ है।</t>
+          <t>हर शब्द को ध्यान से देखिए और सुनिए। किस शब्द में प की आवाज़ आ रही है?</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>page 7 · reveal</t>
+          <t>page 7 · hint</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1047,7 +1053,7 @@
         </is>
       </c>
       <c r="G13" s="4" t="n">
-        <v>27</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14">
@@ -1056,22 +1062,22 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>vo_g2_try</t>
+          <t>vo_g2_more</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>vo_g2_try.wav</t>
+          <t>vo_g2_more.wav</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>इस शब्द की शुरुआत में प की आवाज़ नहीं है। एक बार फिर सुनो।</t>
+          <t>एक और प वाले शब्द पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>page 7 · try_again</t>
+          <t>page 7 · more</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -1080,7 +1086,7 @@
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>58</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15">
@@ -1089,31 +1095,31 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>vo_g3_correct</t>
+          <t>vo_g2_prompt</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>vo_g3_correct.wav</t>
+          <t>vo_g2_prompt.wav</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>चूहे, चार, चने, चबाए — इन सब शब्दों में च की आवाज़ बार-बार आई।</t>
+          <t>“प” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>page 10 · correct</t>
+          <t>page 7 · prompt</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>delivered - do NOT re-record</t>
+          <t>RE-RECORD - build differs from the delivered take</t>
         </is>
       </c>
       <c r="G15" s="4" t="n">
-        <v>62</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">
@@ -1122,22 +1128,22 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>vo_g3_prompt</t>
+          <t>vo_g2_reveal</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>vo_g3_prompt.wav</t>
+          <t>vo_g2_reveal.wav</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>इस वाक्य में कौन-सी आवाज़ बार-बार आई?</t>
+          <t>सुनो — इसमें प की आवाज़ है।</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>page 10 · prompt</t>
+          <t>page 7 · reveal</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -1146,7 +1152,7 @@
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17">
@@ -1155,22 +1161,22 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>vo_g3_reveal</t>
+          <t>vo_g2_try</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>vo_g3_reveal.wav</t>
+          <t>vo_g2_try.wav</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>ध्यान से देखिए, सही जवाब च है।</t>
+          <t>इस शब्द की शुरुआत में प की आवाज़ नहीं है। एक बार फिर सुनो।</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>page 10 · reveal</t>
+          <t>page 7 · try_again</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1179,7 +1185,7 @@
         </is>
       </c>
       <c r="G17" s="4" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18">
@@ -1188,22 +1194,22 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>vo_g3_try</t>
+          <t>vo_g3_correct</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>vo_g3_try.wav</t>
+          <t>vo_g3_correct.wav</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>यह च की आवाज़ नहीं है।</t>
+          <t>चूहे, चार, चने, चबाए — इन सब शब्दों में च की आवाज़ बार-बार आई।</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>page 10 · try_again</t>
+          <t>page 10 · correct</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1212,7 +1218,7 @@
         </is>
       </c>
       <c r="G18" s="4" t="n">
-        <v>22</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
@@ -1221,31 +1227,31 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>vo_g5_correct</t>
+          <t>vo_g3_h1</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>vo_g5_correct.wav</t>
+          <t>vo_g3_h1.wav</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>बहुत बढ़िया! सही डिब्बा।</t>
+          <t>फिर से सुनिए। वाक्य ध्यान से सुनिए और देखिए कौन-सी आवाज़ बार-बार आ रही है।</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>page 12 · correct; page 12 · correct (2nd half)</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>delivered - do NOT re-record</t>
+          <t>page 10 · h1</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
         </is>
       </c>
       <c r="G19" s="4" t="n">
-        <v>24</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20">
@@ -1254,31 +1260,31 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>vo_g5_hint</t>
+          <t>vo_g3_h2</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>vo_g5_hint.wav</t>
+          <t>vo_g3_h2.wav</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>शब्द बोलो और सुनो — उसमें प की आवाज़ है या च की?</t>
+          <t>सुनिए, कौन-सी आवाज़ बार-बार आ रही है? उसी अक्षर पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>page 12 · hint (2nd half)</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>delivered - do NOT re-record</t>
+          <t>page 10 · h2</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21">
@@ -1287,31 +1293,31 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>vo_g5_prompt</t>
+          <t>vo_g3_h3</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>vo_g5_prompt.wav</t>
+          <t>vo_g3_h3.wav</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>हर चित्र का नाम सुनिए और उसे सही डिब्बे में डालिए।</t>
+          <t>चूहे, चार, चने, चबाए… इन सबमें ‘च’ की आवाज़ है। ‘च’ पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>page 12 · prompt (2nd half)</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>delivered - do NOT re-record</t>
+          <t>page 10 · h3</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
         </is>
       </c>
       <c r="G21" s="4" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22">
@@ -1320,22 +1326,22 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>vo_g5_show</t>
+          <t>vo_g3_prompt</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>vo_g5_show.wav</t>
+          <t>vo_g3_prompt.wav</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>हर चित्र को उसके सही डिब्बे में ऐसे डालते हैं।</t>
+          <t>इस वाक्य में कौन-सी आवाज़ बार-बार आई?</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>page 12 · prompt</t>
+          <t>page 10 · prompt</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1344,7 +1350,7 @@
         </is>
       </c>
       <c r="G22" s="4" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23">
@@ -1353,22 +1359,22 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>vo_g5_try</t>
+          <t>vo_g3_reveal</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>vo_g5_try.wav</t>
+          <t>vo_g3_reveal.wav</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>यह डिब्बा सही नहीं है। शब्द की आवाज़ फिर सुनो।</t>
+          <t>ध्यान से देखिए, सही जवाब च है।</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>page 12 · try_again (2nd half)</t>
+          <t>page 10 · reveal</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1377,7 +1383,7 @@
         </is>
       </c>
       <c r="G23" s="4" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24">
@@ -1386,22 +1392,22 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>vo_line_l1</t>
+          <t>vo_g3_try</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>vo_line_l1.wav</t>
+          <t>vo_g3_try.wav</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>पीतल के पतीले में पपीता पीला-पीला।</t>
+          <t>यह च की आवाज़ नहीं है।</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>page 5 · prompt; page 5 · whole line</t>
+          <t>page 10 · try_again</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1410,7 +1416,7 @@
         </is>
       </c>
       <c r="G24" s="4" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -1419,22 +1425,22 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>vo_line_l2</t>
+          <t>vo_g5_correct</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>vo_line_l2.wav</t>
+          <t>vo_g5_correct.wav</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>चूहे ने चार चने चबाए।</t>
+          <t>बहुत बढ़िया! सही डिब्बा।</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>page 1 · prompt; page 1 · whole line; page 10 · whole line</t>
+          <t>page 12 · correct; page 12 · correct (2nd half)</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1443,7 +1449,7 @@
         </is>
       </c>
       <c r="G25" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26">
@@ -1452,31 +1458,31 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>vo_line_l3</t>
+          <t>vo_g5_h1</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>vo_line_l3.wav</t>
+          <t>vo_g5_h1.wav</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>मेरे मामा मीठी मलाई लाए।</t>
+          <t>फिर से सुनिए। चित्र का नाम ध्यान से सुनिए और देखिए उसकी शुरुआत किस आवाज़ से होती है।</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>page 3 · prompt; page 3 · whole line</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>delivered - do NOT re-record</t>
+          <t>page 12 · h1 (2nd half)</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
         </is>
       </c>
       <c r="G26" s="4" t="n">
-        <v>24</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27">
@@ -1485,22 +1491,22 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>vo_line_l6</t>
+          <t>vo_g5_hint</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>vo_line_l6.wav</t>
+          <t>vo_g5_hint.wav</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>नानी ने नई नाव बनाई।</t>
+          <t>शब्द बोलो और सुनो — उसमें प की आवाज़ है या च की?</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>page 11 · whole line</t>
+          <t>page 12 · hint (2nd half)</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1509,7 +1515,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28">
@@ -1518,31 +1524,31 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_ch</t>
+          <t>vo_g5_prompt</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_ch.wav</t>
+          <t>vo_g5_prompt.wav</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>च</t>
+          <t>हर चित्र का नाम सुनिए और उसे सही डिब्बे में डालिए।</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>page 1 · target; page 1 · option च; page 10 · target; page 10 · option च</t>
+          <t>page 12 · prompt (2nd half)</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29">
@@ -1551,31 +1557,31 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_l</t>
+          <t>vo_g5_show</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_l.wav</t>
+          <t>vo_g5_show.wav</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>ल</t>
+          <t>हर चित्र को उसके सही डिब्बे में ऐसे डालते हैं।</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>page 10 · option ल; page 11 · option ल</t>
+          <t>page 12 · prompt</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30">
@@ -1584,31 +1590,31 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_m</t>
+          <t>vo_g5_try</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_m.wav</t>
+          <t>vo_g5_try.wav</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>म</t>
+          <t>यह डिब्बा सही नहीं है। शब्द की आवाज़ फिर सुनो।</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>page 3 · target; page 3 · option म; page 11 · option म</t>
+          <t>page 12 · try_again (2nd half)</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31">
@@ -1617,31 +1623,31 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_n</t>
+          <t>vo_line_l1</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_n.wav</t>
+          <t>vo_line_l1.wav</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>न</t>
+          <t>पीतल के पतीले में पपीता पीला-पीला।</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>page 11 · target; page 11 · option न</t>
+          <t>page 5 · prompt; page 5 · whole line</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32">
@@ -1650,31 +1656,31 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_p</t>
+          <t>vo_line_l2</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_p.wav</t>
+          <t>vo_line_l2.wav</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>प</t>
+          <t>चूहे ने चार चने चबाए।</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>page 5 · target; page 5 · option प</t>
+          <t>page 1 · prompt; page 1 · whole line; page 10 · whole line</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33">
@@ -1683,31 +1689,31 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_r</t>
+          <t>vo_line_l3</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_r.wav</t>
+          <t>vo_line_l3.wav</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>र</t>
+          <t>मेरे मामा मीठी मलाई लाए।</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>page 10 · option र</t>
+          <t>page 3 · prompt; page 3 · whole line</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34">
@@ -1716,22 +1722,22 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_done</t>
+          <t>vo_line_l6</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_done.wav</t>
+          <t>vo_line_l6.wav</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>शाबाश! म की आवाज़ वाले सारे शब्द मिल गए।</t>
+          <t>नानी ने नई नाव बनाई।</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>page 8 · done</t>
+          <t>page 11 · whole line</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -1740,7 +1746,7 @@
         </is>
       </c>
       <c r="G34" s="4" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35">
@@ -1749,31 +1755,31 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_hint</t>
+          <t>vo_ltr_ch</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_hint.wav</t>
+          <t>vo_ltr_ch.wav</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>हर शब्द सुनो — क्या उसमें म की आवाज़ सुनाई देती है?</t>
+          <t>च</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>page 8 · hint</t>
+          <t>page 1 · target; page 1 · option च; page 10 · target; page 10 · option च</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>delivered - do NOT re-record</t>
+          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
         </is>
       </c>
       <c r="G35" s="4" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1782,31 +1788,31 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_more</t>
+          <t>vo_ltr_l</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_more.wav</t>
+          <t>vo_ltr_l.wav</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>एक और म वाले शब्द पर टैप कीजिए।</t>
+          <t>ल</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>page 8 · more</t>
+          <t>page 10 · option ल; page 11 · option ल</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>delivered - do NOT re-record</t>
+          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
         </is>
       </c>
       <c r="G36" s="4" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1815,31 +1821,31 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_prompt</t>
+          <t>vo_ltr_m</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_prompt.wav</t>
+          <t>vo_ltr_m.wav</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>“म” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
+          <t>म</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>page 8 · prompt</t>
+          <t>page 3 · target; page 3 · option म; page 11 · option म</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
+          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
         </is>
       </c>
       <c r="G37" s="4" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1848,31 +1854,31 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_reveal</t>
+          <t>vo_ltr_n</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_reveal.wav</t>
+          <t>vo_ltr_n.wav</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>सुनो — इसमें म की आवाज़ है।</t>
+          <t>न</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>page 8 · reveal</t>
+          <t>page 11 · target; page 11 · option न</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>delivered - do NOT re-record</t>
+          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
         </is>
       </c>
       <c r="G38" s="4" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1881,31 +1887,31 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_try</t>
+          <t>vo_ltr_p</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_try.wav</t>
+          <t>vo_ltr_p.wav</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>इस शब्द की शुरुआत में म की आवाज़ नहीं है। एक बार फिर सुनो।</t>
+          <t>प</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>page 8 · try_again</t>
+          <t>page 5 · target; page 5 · option प</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>delivered - do NOT re-record</t>
+          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
         </is>
       </c>
       <c r="G39" s="4" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1914,31 +1920,31 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_correct</t>
+          <t>vo_ltr_r</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_correct.wav</t>
+          <t>vo_ltr_r.wav</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>सही! शुरुआत में न की आवाज़ थी।</t>
+          <t>र</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>page 11 · correct</t>
+          <t>page 10 · option र</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>delivered - do NOT re-record</t>
+          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
         </is>
       </c>
       <c r="G40" s="4" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1947,22 +1953,22 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_prompt</t>
+          <t>vo_p1_done</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_prompt.wav</t>
+          <t>vo_p1_done.wav</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>कौन-सी आवाज़ शब्दों की शुरुआत में बार-बार आई?</t>
+          <t>शाबाश! म की आवाज़ वाले सारे शब्द मिल गए।</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>page 11 · prompt</t>
+          <t>page 8 · done</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -1971,7 +1977,7 @@
         </is>
       </c>
       <c r="G41" s="4" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42">
@@ -1980,31 +1986,31 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_reveal</t>
+          <t>vo_p1_h1</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_reveal.wav</t>
+          <t>vo_p1_h1.wav</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>शुरुआत में न की आवाज़ बार-बार आई।</t>
+          <t>फिर से सुनिए। जिन शब्दों की शुरुआत ‘म’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>page 11 · reveal</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>delivered - do NOT re-record</t>
+          <t>page 8 · h1</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
         </is>
       </c>
       <c r="G42" s="4" t="n">
-        <v>33</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43">
@@ -2013,31 +2019,31 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_try</t>
+          <t>vo_p1_h2</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_try.wav</t>
+          <t>vo_p1_h2.wav</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>तुमने आखिरी आवाज़ सुनी। हमें वह आवाज़ ढूँढनी है जो पूरे वाक्य में बार-बार आई है।</t>
+          <t>जिन शब्दों की शुरुआत ‘म’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>page 11 · try_again</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>delivered - do NOT re-record</t>
+          <t>page 8 · h2</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
         </is>
       </c>
       <c r="G43" s="4" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44">
@@ -2046,31 +2052,31 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_done</t>
+          <t>vo_p1_h3</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_done.wav</t>
+          <t>vo_p1_h3.wav</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>वाह! तुमने च की आवाज़ हर जगह पहचान ली।</t>
+          <t>देखिए, ‘मामा’ और ‘मूली’ की शुरुआत ‘म’ की आवाज़ से होती है। इन पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>page 9 · done</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>delivered - do NOT re-record</t>
+          <t>page 8 · h3</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
         </is>
       </c>
       <c r="G44" s="4" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45">
@@ -2079,22 +2085,22 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_hint</t>
+          <t>vo_p1_hint</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_hint.wav</t>
+          <t>vo_p1_hint.wav</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>च की आवाज़ शुरू में भी हो सकती है और बीच में भी। पूरा शब्द सुनो।</t>
+          <t>हर शब्द सुनो — क्या उसमें म की आवाज़ सुनाई देती है?</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>page 9 · hint</t>
+          <t>page 8 · hint</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -2103,7 +2109,7 @@
         </is>
       </c>
       <c r="G45" s="4" t="n">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="46">
@@ -2112,22 +2118,22 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_more</t>
+          <t>vo_p1_more</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_more.wav</t>
+          <t>vo_p1_more.wav</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>एक और च वाले शब्द पर टैप कीजिए।</t>
+          <t>एक और म वाले शब्द पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>page 9 · more</t>
+          <t>page 8 · more</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -2145,22 +2151,22 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_prompt</t>
+          <t>vo_p1_prompt</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_prompt.wav</t>
+          <t>vo_p1_prompt.wav</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>“च” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
+          <t>“म” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>page 9 · prompt</t>
+          <t>page 8 · prompt</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -2178,22 +2184,22 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_reveal</t>
+          <t>vo_p1_reveal</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_reveal.wav</t>
+          <t>vo_p1_reveal.wav</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>सुनो — इसमें च की आवाज़ है।</t>
+          <t>सुनो — इसमें म की आवाज़ है।</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>page 9 · reveal</t>
+          <t>page 8 · reveal</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -2211,22 +2217,22 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_try</t>
+          <t>vo_p1_try</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_try.wav</t>
+          <t>vo_p1_try.wav</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>इस शब्द में च की आवाज़ कहीं नहीं है। एक बार फिर सुनो।</t>
+          <t>इस शब्द की शुरुआत में म की आवाज़ नहीं है। एक बार फिर सुनो।</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>page 9 · try_again</t>
+          <t>page 8 · try_again</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -2235,7 +2241,7 @@
         </is>
       </c>
       <c r="G49" s="4" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50">
@@ -2244,31 +2250,31 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>vo_p8_prompt</t>
+          <t>vo_p4_correct</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>vo_p8_prompt.wav</t>
+          <t>vo_p4_correct.wav</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>शाबाश! आज हमने सीखा — वाक्य ध्यान से सुनना, बार-बार आने वाली आवाज़ पहचानना, और प, च और म की आवाज़ ढूँढना।</t>
+          <t>सही! शुरुआत में न की आवाज़ थी।</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>page 14 · prompt</t>
+          <t>page 11 · correct</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G50" s="4" t="n">
-        <v>105</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51">
@@ -2277,31 +2283,31 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>vo_snd_ch</t>
+          <t>vo_p4_h1</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>vo_snd_ch.wav</t>
+          <t>vo_p4_h1.wav</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>च से चम्मच।</t>
+          <t>फिर से सुनिए। वाक्य ध्यान से सुनिए और देखिए शब्दों की शुरुआत में कौन-सी आवाज़ बार-बार आ रही है।</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>page 2 · sound; page 9 · target</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
+          <t>page 11 · h1</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
         </is>
       </c>
       <c r="G51" s="4" t="n">
-        <v>11</v>
+        <v>95</v>
       </c>
     </row>
     <row r="52">
@@ -2310,31 +2316,31 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>vo_snd_m</t>
+          <t>vo_p4_h2</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>vo_snd_m.wav</t>
+          <t>vo_p4_h2.wav</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>म से मछली।</t>
+          <t>सुनिए, कौन-सी आवाज़ बार-बार आ रही है? उसी अक्षर पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>page 4 · sound; page 8 · target</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>delivered - do NOT re-record</t>
+          <t>page 11 · h2</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
         </is>
       </c>
       <c r="G52" s="4" t="n">
-        <v>10</v>
+        <v>61</v>
       </c>
     </row>
     <row r="53">
@@ -2343,31 +2349,31 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>vo_snd_p</t>
+          <t>vo_p4_h3</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>vo_snd_p.wav</t>
+          <t>vo_p4_h3.wav</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>प से पतंग।</t>
+          <t>नानी, ने, नई, नाव… इन सबकी शुरुआत ‘न’ की आवाज़ से होती है। ‘न’ पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>page 6 · sound; page 7 · target; page 12 · target; page 12 · target (2nd half) (+1 more)</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>delivered - do NOT re-record</t>
+          <t>page 11 · h3</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
         </is>
       </c>
       <c r="G53" s="4" t="n">
-        <v>10</v>
+        <v>76</v>
       </c>
     </row>
     <row r="54">
@@ -2376,22 +2382,22 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>vo_t1_explain</t>
+          <t>vo_p4_prompt</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>vo_t1_explain.wav</t>
+          <t>vo_p4_prompt.wav</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>पीतल, पतीले, पपीता, पीला-पीला—इन सब शब्दों में प की आवाज़ बार-बार आई।</t>
+          <t>कौन-सी आवाज़ शब्दों की शुरुआत में बार-बार आई?</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>page 5 · teach step 4</t>
+          <t>page 11 · prompt</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -2400,7 +2406,7 @@
         </is>
       </c>
       <c r="G54" s="4" t="n">
-        <v>69</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55">
@@ -2409,22 +2415,22 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>vo_t2_prompt</t>
+          <t>vo_p4_reveal</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>vo_t2_prompt.wav</t>
+          <t>vo_p4_reveal.wav</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>हमने प की आवाज़ सुनी। यह आवाज़ प अक्षर से लिखी जाती है। जैसे—प से पपीता।</t>
+          <t>शुरुआत में न की आवाज़ बार-बार आई।</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>page 6 · prompt</t>
+          <t>page 11 · reveal</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -2433,7 +2439,7 @@
         </is>
       </c>
       <c r="G55" s="4" t="n">
-        <v>72</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56">
@@ -2442,22 +2448,22 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>vo_t3_explain</t>
+          <t>vo_p4_try</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>vo_t3_explain.wav</t>
+          <t>vo_p4_try.wav</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>चूहे, चार, चने, चबाए—इन सब शब्दों में च की आवाज़ बार-बार आई।</t>
+          <t>तुमने आखिरी आवाज़ सुनी। हमें वह आवाज़ ढूँढनी है जो पूरे वाक्य में बार-बार आई है।</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>page 1 · teach step 4</t>
+          <t>page 11 · try_again</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -2466,7 +2472,7 @@
         </is>
       </c>
       <c r="G56" s="4" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57">
@@ -2475,22 +2481,22 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>vo_t4_prompt</t>
+          <t>vo_p7_done</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>vo_t4_prompt.wav</t>
+          <t>vo_p7_done.wav</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>हमने च की आवाज़ सुनी। यह आवाज़ च अक्षर से लिखी जाती है। जैसे—च से चूहा।</t>
+          <t>वाह! तुमने च की आवाज़ हर जगह पहचान ली।</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>page 2 · prompt</t>
+          <t>page 9 · done</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -2499,7 +2505,7 @@
         </is>
       </c>
       <c r="G57" s="4" t="n">
-        <v>71</v>
+        <v>38</v>
       </c>
     </row>
     <row r="58">
@@ -2508,31 +2514,31 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>vo_t5_explain</t>
+          <t>vo_p7_h1</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>vo_t5_explain.wav</t>
+          <t>vo_p7_h1.wav</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>मेरे, मामा, मीठी, मलाई—इन सब शब्दों में म की आवाज़ बार-बार आई।</t>
+          <t>फिर से सुनिए। जिन शब्दों की शुरुआत ‘च’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>page 3 · teach step 4</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>delivered - do NOT re-record</t>
+          <t>page 9 · h1</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
         </is>
       </c>
       <c r="G58" s="4" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
     </row>
     <row r="59">
@@ -2541,31 +2547,31 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>vo_t6_prompt</t>
+          <t>vo_p7_h2</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>vo_t6_prompt.wav</t>
+          <t>vo_p7_h2.wav</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>हमने म की आवाज़ सुनी। यह आवाज़ म अक्षर से लिखी जाती है। जैसे—म से मूली।</t>
+          <t>जिन शब्दों की शुरुआत ‘च’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>page 4 · prompt</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>delivered - do NOT re-record</t>
+          <t>page 9 · h2</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
         </is>
       </c>
       <c r="G59" s="4" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="60">
@@ -2574,31 +2580,31 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>vo_w_aam</t>
+          <t>vo_p7_h3</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>vo_w_aam.wav</t>
+          <t>vo_p7_h3.wav</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>आम</t>
+          <t>देखिए, ‘चाँद’ और ‘चश्मा’ की शुरुआत ‘च’ की आवाज़ से होती है। इन पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>page 7 · picture आम; page 13 · round 1 balloon आम; page 13 · round 2 refill आम</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>delivered - do NOT re-record</t>
+          <t>page 9 · h3</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
         </is>
       </c>
       <c r="G60" s="4" t="n">
-        <v>2</v>
+        <v>76</v>
       </c>
     </row>
     <row r="61">
@@ -2607,22 +2613,22 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chammach</t>
+          <t>vo_p7_hint</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chammach.wav</t>
+          <t>vo_p7_hint.wav</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>चम्मच</t>
+          <t>च की आवाज़ शुरू में भी हो सकती है और बीच में भी। पूरा शब्द सुनो।</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>page 12 · picture चम्मच (2nd half); page 13 · round 2 balloon चम्मच</t>
+          <t>page 9 · hint</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -2631,7 +2637,7 @@
         </is>
       </c>
       <c r="G61" s="4" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="62">
@@ -2640,22 +2646,22 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chand</t>
+          <t>vo_p7_more</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chand.wav</t>
+          <t>vo_p7_more.wav</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>चाँद</t>
+          <t>एक और च वाले शब्द पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>page 9 · picture चाँद; page 12 · picture चाँद; page 13 · round 2 balloon चाँद</t>
+          <t>page 9 · more</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -2664,7 +2670,7 @@
         </is>
       </c>
       <c r="G62" s="4" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
     </row>
     <row r="63">
@@ -2673,31 +2679,31 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chashma</t>
+          <t>vo_p7_prompt</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chashma.wav</t>
+          <t>vo_p7_prompt.wav</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>चश्मा</t>
+          <t>“च” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>page 9 · picture चश्मा</t>
+          <t>page 9 · prompt</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>delivered - do NOT re-record</t>
+          <t>RE-RECORD - build differs from the delivered take</t>
         </is>
       </c>
       <c r="G63" s="4" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="64">
@@ -2706,22 +2712,22 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chidiya</t>
+          <t>vo_p7_reveal</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chidiya.wav</t>
+          <t>vo_p7_reveal.wav</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>चिड़िया</t>
+          <t>सुनो — इसमें च की आवाज़ है।</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>page 8 · picture चिड़िया</t>
+          <t>page 9 · reveal</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -2730,7 +2736,7 @@
         </is>
       </c>
       <c r="G64" s="4" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65">
@@ -2739,22 +2745,22 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chinti</t>
+          <t>vo_p7_try</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chinti.wav</t>
+          <t>vo_p7_try.wav</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>चींटी</t>
+          <t>इस शब्द में च की आवाज़ कहीं नहीं है। एक बार फिर सुनो।</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>page 13 · round 2 balloon चींटी</t>
+          <t>page 9 · try_again</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -2763,7 +2769,7 @@
         </is>
       </c>
       <c r="G65" s="4" t="n">
-        <v>5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66">
@@ -2772,31 +2778,31 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chuha</t>
+          <t>vo_p8_prompt</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chuha.wav</t>
+          <t>vo_p8_prompt.wav</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>चूहा</t>
+          <t>शाबाश! आज हमने सीखा — वाक्य ध्यान से सुनना, बार-बार आने वाली आवाज़ पहचानना, और प, च और म की आवाज़ ढूँढना।</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>page 2 · word_name; page 12 · picture चूहा (2nd half); page 13 · round 2 balloon चूहा</t>
+          <t>page 14 · prompt</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>delivered - do NOT re-record</t>
+          <t>RE-RECORD - build differs from the delivered take</t>
         </is>
       </c>
       <c r="G66" s="4" t="n">
-        <v>4</v>
+        <v>105</v>
       </c>
     </row>
     <row r="67">
@@ -2805,31 +2811,31 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>vo_w_ghar</t>
+          <t>vo_snd_ch</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>vo_w_ghar.wav</t>
+          <t>vo_snd_ch.wav</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>घर</t>
+          <t>च से चम्मच।</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>page 13 · round 1 balloon घर; page 13 · round 2 refill घर</t>
+          <t>page 2 · sound; page 9 · target</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>delivered - do NOT re-record</t>
+          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
         </is>
       </c>
       <c r="G67" s="4" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68">
@@ -2838,22 +2844,22 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kabutar</t>
+          <t>vo_snd_m</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kabutar.wav</t>
+          <t>vo_snd_m.wav</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>कबूतर</t>
+          <t>म से मछली।</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>page 13 · round 2 balloon कबूतर</t>
+          <t>page 4 · sound; page 8 · target</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -2862,7 +2868,7 @@
         </is>
       </c>
       <c r="G68" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69">
@@ -2871,31 +2877,31 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kamal</t>
+          <t>vo_snd_p</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kamal.wav</t>
+          <t>vo_snd_p.wav</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>कमल</t>
+          <t>प से पतंग।</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>page 13 · round 2 balloon कमल</t>
+          <t>page 6 · sound; page 7 · target; page 12 · target; page 12 · target (2nd half) (+1 more)</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G69" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70">
@@ -2904,22 +2910,22 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kauaa</t>
+          <t>vo_t1_explain</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kauaa.wav</t>
+          <t>vo_t1_explain.wav</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>कौआ</t>
+          <t>पीतल, पतीले, पपीता, पीला-पीला—इन सब शब्दों में प की आवाज़ बार-बार आई।</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>page 13 · round 2 balloon कौआ</t>
+          <t>page 5 · teach step 4</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -2928,7 +2934,7 @@
         </is>
       </c>
       <c r="G70" s="4" t="n">
-        <v>3</v>
+        <v>69</v>
       </c>
     </row>
     <row r="71">
@@ -2937,22 +2943,22 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kela</t>
+          <t>vo_t2_prompt</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kela.wav</t>
+          <t>vo_t2_prompt.wav</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>केला</t>
+          <t>हमने प की आवाज़ सुनी। यह आवाज़ प अक्षर से लिखी जाती है। जैसे—प से पपीता।</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>page 7 · picture केला; page 13 · round 1 balloon केला; page 13 · round 2 balloon केला</t>
+          <t>page 6 · prompt</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -2961,7 +2967,7 @@
         </is>
       </c>
       <c r="G71" s="4" t="n">
-        <v>4</v>
+        <v>72</v>
       </c>
     </row>
     <row r="72">
@@ -2970,22 +2976,22 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>vo_w_laal</t>
+          <t>vo_t3_explain</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>vo_w_laal.wav</t>
+          <t>vo_t3_explain.wav</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>लाल</t>
+          <t>चूहे, चार, चने, चबाए—इन सब शब्दों में च की आवाज़ बार-बार आई।</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>page 9 · picture लाल; page 13 · round 1 refill लाल</t>
+          <t>page 1 · teach step 4</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -2994,7 +3000,7 @@
         </is>
       </c>
       <c r="G72" s="4" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="73">
@@ -3003,22 +3009,22 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>vo_w_laddu</t>
+          <t>vo_t4_prompt</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>vo_w_laddu.wav</t>
+          <t>vo_t4_prompt.wav</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>लड्डू</t>
+          <t>हमने च की आवाज़ सुनी। यह आवाज़ च अक्षर से लिखी जाती है। जैसे—च से चूहा।</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>page 8 · picture लड्डू</t>
+          <t>page 2 · prompt</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -3027,7 +3033,7 @@
         </is>
       </c>
       <c r="G73" s="4" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
     </row>
     <row r="74">
@@ -3036,22 +3042,22 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>vo_w_machhli</t>
+          <t>vo_t5_explain</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>vo_w_machhli.wav</t>
+          <t>vo_t5_explain.wav</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>मछली</t>
+          <t>मेरे, मामा, मीठी, मलाई—इन सब शब्दों में म की आवाज़ बार-बार आई।</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>page 13 · round 1 balloon मछली; page 13 · round 2 refill मछली</t>
+          <t>page 3 · teach step 4</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -3060,7 +3066,7 @@
         </is>
       </c>
       <c r="G74" s="4" t="n">
-        <v>4</v>
+        <v>62</v>
       </c>
     </row>
     <row r="75">
@@ -3069,22 +3075,22 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>vo_w_mala</t>
+          <t>vo_t6_prompt</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>vo_w_mala.wav</t>
+          <t>vo_t6_prompt.wav</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>माला</t>
+          <t>हमने म की आवाज़ सुनी। यह आवाज़ म अक्षर से लिखी जाती है। जैसे—म से मूली।</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>page 9 · picture माला; page 13 · round 1 refill माला</t>
+          <t>page 4 · prompt</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -3093,7 +3099,7 @@
         </is>
       </c>
       <c r="G75" s="4" t="n">
-        <v>4</v>
+        <v>71</v>
       </c>
     </row>
     <row r="76">
@@ -3102,22 +3108,22 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>vo_w_mama</t>
+          <t>vo_w_aam</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>vo_w_mama.wav</t>
+          <t>vo_w_aam.wav</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>मामा</t>
+          <t>आम</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>page 8 · picture मामा</t>
+          <t>page 7 · picture आम; page 13 · round 1 balloon आम; page 13 · round 2 refill आम</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -3126,7 +3132,7 @@
         </is>
       </c>
       <c r="G76" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -3135,22 +3141,22 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>vo_w_muli</t>
+          <t>vo_w_chammach</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>vo_w_muli.wav</t>
+          <t>vo_w_chammach.wav</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>मूली</t>
+          <t>चम्मच</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>page 4 · word_name; page 8 · picture मूली; page 13 · round 1 refill मूली</t>
+          <t>page 12 · picture चम्मच (2nd half); page 13 · round 2 balloon चम्मच</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -3159,7 +3165,7 @@
         </is>
       </c>
       <c r="G77" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
@@ -3168,22 +3174,22 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>vo_w_pani</t>
+          <t>vo_w_chand</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>vo_w_pani.wav</t>
+          <t>vo_w_chand.wav</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>पानी</t>
+          <t>चाँद</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>page 12 · picture पानी (2nd half); page 13 · round 1 balloon पानी</t>
+          <t>page 9 · picture चाँद; page 12 · picture चाँद; page 13 · round 2 balloon चाँद</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -3201,22 +3207,22 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>vo_w_papita</t>
+          <t>vo_w_chashma</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>vo_w_papita.wav</t>
+          <t>vo_w_chashma.wav</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>पपीता</t>
+          <t>चश्मा</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>page 6 · word_name; page 7 · picture पपीता; page 13 · round 1 balloon पपीता</t>
+          <t>page 9 · picture चश्मा</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -3234,22 +3240,22 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>vo_w_patang</t>
+          <t>vo_w_chidiya</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>vo_w_patang.wav</t>
+          <t>vo_w_chidiya.wav</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>पतंग</t>
+          <t>चिड़िया</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>page 7 · picture पतंग; page 12 · picture पतंग; page 13 · round 1 balloon पतंग</t>
+          <t>page 8 · picture चिड़िया</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -3258,7 +3264,7 @@
         </is>
       </c>
       <c r="G80" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81">
@@ -3267,22 +3273,22 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>vo_w_patta</t>
+          <t>vo_w_chinti</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>vo_w_patta.wav</t>
+          <t>vo_w_chinti.wav</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>पत्ता</t>
+          <t>चींटी</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>page 13 · round 1 balloon पत्ता</t>
+          <t>page 13 · round 2 balloon चींटी</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -3300,30 +3306,558 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
+          <t>vo_w_chuha</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_chuha.wav</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>चूहा</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>page 2 · word_name; page 12 · picture चूहा (2nd half); page 13 · round 2 balloon चूहा</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_ghar</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_ghar.wav</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>घर</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>page 13 · round 1 balloon घर; page 13 · round 2 refill घर</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_kabutar</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_kabutar.wav</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>कबूतर</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>page 13 · round 2 balloon कबूतर</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_kamal</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_kamal.wav</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>कमल</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>page 13 · round 2 balloon कमल</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>RE-RECORD - build differs from the delivered take</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_kauaa</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_kauaa.wav</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>कौआ</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>page 13 · round 2 balloon कौआ</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_kela</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_kela.wav</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>केला</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>page 7 · picture केला; page 13 · round 1 balloon केला; page 13 · round 2 balloon केला</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_laal</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_laal.wav</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>लाल</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>page 9 · picture लाल; page 13 · round 1 refill लाल</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_laddu</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_laddu.wav</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>लड्डू</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>page 8 · picture लड्डू</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_machhli</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_machhli.wav</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>मछली</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>page 13 · round 1 balloon मछली; page 13 · round 2 refill मछली</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_mala</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_mala.wav</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>माला</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>page 9 · picture माला; page 13 · round 1 refill माला</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_mama</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_mama.wav</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>मामा</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>page 8 · picture मामा</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_muli</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_muli.wav</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>मूली</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>page 4 · word_name; page 8 · picture मूली; page 13 · round 1 refill मूली</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_pani</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_pani.wav</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>पानी</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>page 12 · picture पानी (2nd half); page 13 · round 1 balloon पानी</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_papita</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_papita.wav</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>पपीता</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>page 6 · word_name; page 7 · picture पपीता; page 13 · round 1 balloon पपीता</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_patang</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_patang.wav</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>पतंग</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>page 7 · picture पतंग; page 12 · picture पतंग; page 13 · round 1 balloon पतंग</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_patta</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>vo_w_patta.wav</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>पत्ता</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>page 13 · round 1 balloon पत्ता</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
           <t>vo_w_payal</t>
         </is>
       </c>
-      <c r="C82" s="4" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>vo_w_payal.wav</t>
         </is>
       </c>
-      <c r="D82" s="5" t="inlineStr">
+      <c r="D98" s="5" t="inlineStr">
         <is>
           <t>पायल</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
+      <c r="E98" s="4" t="inlineStr">
         <is>
           <t>page 12 · picture पायल (2nd half)</t>
         </is>
       </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>delivered - do NOT re-record</t>
-        </is>
-      </c>
-      <c r="G82" s="4" t="n">
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="n">
         <v>4</v>
       </c>
     </row>

--- a/build/assets/Audio/audio_manifest.xlsx
+++ b/build/assets/Audio/audio_manifest.xlsx
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D2" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E2" t="n">
         <v>16</v>
@@ -611,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>page 12 · prompt (2nd half)</t>
+          <t>page 12 · prompt; page 12 · prompt (2nd half)</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1557,22 +1557,22 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>vo_g5_show</t>
+          <t>vo_g5_try</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>vo_g5_show.wav</t>
+          <t>vo_g5_try.wav</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>हर चित्र को उसके सही डिब्बे में ऐसे डालते हैं।</t>
+          <t>यह डिब्बा सही नहीं है। शब्द की आवाज़ फिर सुनो।</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>page 12 · prompt</t>
+          <t>page 12 · try_again (2nd half)</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1590,22 +1590,22 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>vo_g5_try</t>
+          <t>vo_line_l1</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>vo_g5_try.wav</t>
+          <t>vo_line_l1.wav</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>यह डिब्बा सही नहीं है। शब्द की आवाज़ फिर सुनो।</t>
+          <t>पीतल के पतीले में पपीता पीला-पीला।</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>page 12 · try_again (2nd half)</t>
+          <t>page 5 · prompt; page 5 · whole line</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="G30" s="4" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31">
@@ -1623,22 +1623,22 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>vo_line_l1</t>
+          <t>vo_line_l2</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>vo_line_l1.wav</t>
+          <t>vo_line_l2.wav</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>पीतल के पतीले में पपीता पीला-पीला।</t>
+          <t>चूहे ने चार चने चबाए।</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>page 5 · prompt; page 5 · whole line</t>
+          <t>page 1 · prompt; page 1 · whole line; page 10 · whole line</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="G31" s="4" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32">
@@ -1656,22 +1656,22 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>vo_line_l2</t>
+          <t>vo_line_l3</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>vo_line_l2.wav</t>
+          <t>vo_line_l3.wav</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>चूहे ने चार चने चबाए।</t>
+          <t>मेरे मामा मीठी मलाई लाए।</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>page 1 · prompt; page 1 · whole line; page 10 · whole line</t>
+          <t>page 3 · prompt; page 3 · whole line</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="G32" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33">
@@ -1689,22 +1689,22 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>vo_line_l3</t>
+          <t>vo_line_l6</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>vo_line_l3.wav</t>
+          <t>vo_line_l6.wav</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>मेरे मामा मीठी मलाई लाए।</t>
+          <t>नानी ने नई नाव बनाई।</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>page 3 · prompt; page 3 · whole line</t>
+          <t>page 11 · whole line</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="G33" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
@@ -1722,31 +1722,31 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>vo_line_l6</t>
+          <t>vo_ltr_ch</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>vo_line_l6.wav</t>
+          <t>vo_ltr_ch.wav</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>नानी ने नई नाव बनाई।</t>
+          <t>च</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>page 11 · whole line</t>
+          <t>page 1 · target; page 1 · option च; page 10 · target; page 10 · option च</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>delivered - do NOT re-record</t>
+          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
         </is>
       </c>
       <c r="G34" s="4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1755,22 +1755,22 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_ch</t>
+          <t>vo_ltr_l</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_ch.wav</t>
+          <t>vo_ltr_l.wav</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>च</t>
+          <t>ल</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>page 1 · target; page 1 · option च; page 10 · target; page 10 · option च</t>
+          <t>page 10 · option ल; page 11 · option ल</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -1788,22 +1788,22 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_l</t>
+          <t>vo_ltr_m</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_l.wav</t>
+          <t>vo_ltr_m.wav</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>ल</t>
+          <t>म</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>page 10 · option ल; page 11 · option ल</t>
+          <t>page 3 · target; page 3 · option म; page 11 · option म</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -1821,22 +1821,22 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_m</t>
+          <t>vo_ltr_n</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_m.wav</t>
+          <t>vo_ltr_n.wav</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>म</t>
+          <t>न</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>page 3 · target; page 3 · option म; page 11 · option म</t>
+          <t>page 11 · target; page 11 · option न</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -1854,22 +1854,22 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_n</t>
+          <t>vo_ltr_p</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_n.wav</t>
+          <t>vo_ltr_p.wav</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>न</t>
+          <t>प</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>page 11 · target; page 11 · option न</t>
+          <t>page 5 · target; page 5 · option प</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -1887,22 +1887,22 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_p</t>
+          <t>vo_ltr_r</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_p.wav</t>
+          <t>vo_ltr_r.wav</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>प</t>
+          <t>र</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>page 5 · target; page 5 · option प</t>
+          <t>page 10 · option र</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -1920,31 +1920,31 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_r</t>
+          <t>vo_p1_done</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_r.wav</t>
+          <t>vo_p1_done.wav</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>र</t>
+          <t>शाबाश! म की आवाज़ वाले सारे शब्द मिल गए।</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>page 10 · option र</t>
+          <t>page 8 · done</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G40" s="4" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41">
@@ -1953,31 +1953,31 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_done</t>
+          <t>vo_p1_h1</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_done.wav</t>
+          <t>vo_p1_h1.wav</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>शाबाश! म की आवाज़ वाले सारे शब्द मिल गए।</t>
+          <t>फिर से सुनिए। जिन शब्दों की शुरुआत ‘म’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>page 8 · done</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>delivered - do NOT re-record</t>
+          <t>page 8 · h1</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
         </is>
       </c>
       <c r="G41" s="4" t="n">
-        <v>40</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42">
@@ -1986,22 +1986,22 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_h1</t>
+          <t>vo_p1_h2</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_h1.wav</t>
+          <t>vo_p1_h2.wav</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>फिर से सुनिए। जिन शब्दों की शुरुआत ‘म’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
+          <t>जिन शब्दों की शुरुआत ‘म’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>page 8 · h1</t>
+          <t>page 8 · h2</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="G42" s="4" t="n">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43">
@@ -2019,22 +2019,22 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_h2</t>
+          <t>vo_p1_h3</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_h2.wav</t>
+          <t>vo_p1_h3.wav</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>जिन शब्दों की शुरुआत ‘म’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
+          <t>देखिए, ‘मामा’ और ‘मूली’ की शुरुआत ‘म’ की आवाज़ से होती है। इन पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>page 8 · h2</t>
+          <t>page 8 · h3</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="G43" s="4" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
     </row>
     <row r="44">
@@ -2052,31 +2052,31 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_h3</t>
+          <t>vo_p1_hint</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_h3.wav</t>
+          <t>vo_p1_hint.wav</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>देखिए, ‘मामा’ और ‘मूली’ की शुरुआत ‘म’ की आवाज़ से होती है। इन पर टैप कीजिए।</t>
+          <t>हर शब्द सुनो — क्या उसमें म की आवाज़ सुनाई देती है?</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>page 8 · h3</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+          <t>page 8 · hint</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G44" s="4" t="n">
-        <v>75</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45">
@@ -2085,22 +2085,22 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_hint</t>
+          <t>vo_p1_more</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_hint.wav</t>
+          <t>vo_p1_more.wav</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>हर शब्द सुनो — क्या उसमें म की आवाज़ सुनाई देती है?</t>
+          <t>एक और म वाले शब्द पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>page 8 · hint</t>
+          <t>page 8 · more</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="G45" s="4" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46">
@@ -2118,31 +2118,31 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_more</t>
+          <t>vo_p1_prompt</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_more.wav</t>
+          <t>vo_p1_prompt.wav</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>एक और म वाले शब्द पर टैप कीजिए।</t>
+          <t>“म” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>page 8 · more</t>
+          <t>page 8 · prompt</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>delivered - do NOT re-record</t>
+          <t>RE-RECORD - build differs from the delivered take</t>
         </is>
       </c>
       <c r="G46" s="4" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47">
@@ -2151,31 +2151,31 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_prompt</t>
+          <t>vo_p1_reveal</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_prompt.wav</t>
+          <t>vo_p1_reveal.wav</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>“म” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
+          <t>सुनो — इसमें म की आवाज़ है।</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>page 8 · prompt</t>
+          <t>page 8 · reveal</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G47" s="4" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48">
@@ -2184,22 +2184,22 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_reveal</t>
+          <t>vo_p1_try</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_reveal.wav</t>
+          <t>vo_p1_try.wav</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>सुनो — इसमें म की आवाज़ है।</t>
+          <t>इस शब्द की शुरुआत में म की आवाज़ नहीं है। एक बार फिर सुनो।</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>page 8 · reveal</t>
+          <t>page 8 · try_again</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="G48" s="4" t="n">
-        <v>27</v>
+        <v>58</v>
       </c>
     </row>
     <row r="49">
@@ -2217,22 +2217,22 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_try</t>
+          <t>vo_p4_correct</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_try.wav</t>
+          <t>vo_p4_correct.wav</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>इस शब्द की शुरुआत में म की आवाज़ नहीं है। एक बार फिर सुनो।</t>
+          <t>सही! शुरुआत में न की आवाज़ थी।</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>page 8 · try_again</t>
+          <t>page 11 · correct</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="G49" s="4" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50">
@@ -2250,31 +2250,31 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_correct</t>
+          <t>vo_p4_h1</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_correct.wav</t>
+          <t>vo_p4_h1.wav</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>सही! शुरुआत में न की आवाज़ थी।</t>
+          <t>फिर से सुनिए। वाक्य ध्यान से सुनिए और देखिए शब्दों की शुरुआत में कौन-सी आवाज़ बार-बार आ रही है।</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>page 11 · correct</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>delivered - do NOT re-record</t>
+          <t>page 11 · h1</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
         </is>
       </c>
       <c r="G50" s="4" t="n">
-        <v>30</v>
+        <v>95</v>
       </c>
     </row>
     <row r="51">
@@ -2283,22 +2283,22 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_h1</t>
+          <t>vo_p4_h2</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_h1.wav</t>
+          <t>vo_p4_h2.wav</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>फिर से सुनिए। वाक्य ध्यान से सुनिए और देखिए शब्दों की शुरुआत में कौन-सी आवाज़ बार-बार आ रही है।</t>
+          <t>सुनिए, कौन-सी आवाज़ बार-बार आ रही है? उसी अक्षर पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>page 11 · h1</t>
+          <t>page 11 · h2</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="G51" s="4" t="n">
-        <v>95</v>
+        <v>61</v>
       </c>
     </row>
     <row r="52">
@@ -2316,22 +2316,22 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_h2</t>
+          <t>vo_p4_h3</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_h2.wav</t>
+          <t>vo_p4_h3.wav</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>सुनिए, कौन-सी आवाज़ बार-बार आ रही है? उसी अक्षर पर टैप कीजिए।</t>
+          <t>नानी, ने, नई, नाव… इन सबकी शुरुआत ‘न’ की आवाज़ से होती है। ‘न’ पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>page 11 · h2</t>
+          <t>page 11 · h3</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="G52" s="4" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
     </row>
     <row r="53">
@@ -2349,31 +2349,31 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_h3</t>
+          <t>vo_p4_prompt</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_h3.wav</t>
+          <t>vo_p4_prompt.wav</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>नानी, ने, नई, नाव… इन सबकी शुरुआत ‘न’ की आवाज़ से होती है। ‘न’ पर टैप कीजिए।</t>
+          <t>कौन-सी आवाज़ शब्दों की शुरुआत में बार-बार आई?</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>page 11 · h3</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+          <t>page 11 · prompt</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G53" s="4" t="n">
-        <v>76</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54">
@@ -2382,22 +2382,22 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_prompt</t>
+          <t>vo_p4_reveal</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_prompt.wav</t>
+          <t>vo_p4_reveal.wav</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>कौन-सी आवाज़ शब्दों की शुरुआत में बार-बार आई?</t>
+          <t>शुरुआत में न की आवाज़ बार-बार आई।</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>page 11 · prompt</t>
+          <t>page 11 · reveal</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="G54" s="4" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55">
@@ -2415,22 +2415,22 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_reveal</t>
+          <t>vo_p4_try</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_reveal.wav</t>
+          <t>vo_p4_try.wav</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>शुरुआत में न की आवाज़ बार-बार आई।</t>
+          <t>तुमने आखिरी आवाज़ सुनी। हमें वह आवाज़ ढूँढनी है जो पूरे वाक्य में बार-बार आई है।</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>page 11 · reveal</t>
+          <t>page 11 · try_again</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="G55" s="4" t="n">
-        <v>33</v>
+        <v>80</v>
       </c>
     </row>
     <row r="56">
@@ -2448,22 +2448,22 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_try</t>
+          <t>vo_p7_done</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_try.wav</t>
+          <t>vo_p7_done.wav</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>तुमने आखिरी आवाज़ सुनी। हमें वह आवाज़ ढूँढनी है जो पूरे वाक्य में बार-बार आई है।</t>
+          <t>वाह! तुमने च की आवाज़ हर जगह पहचान ली।</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>page 11 · try_again</t>
+          <t>page 9 · done</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="G56" s="4" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
     </row>
     <row r="57">
@@ -2481,31 +2481,31 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_done</t>
+          <t>vo_p7_h1</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_done.wav</t>
+          <t>vo_p7_h1.wav</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>वाह! तुमने च की आवाज़ हर जगह पहचान ली।</t>
+          <t>फिर से सुनिए। जिन शब्दों की शुरुआत ‘च’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>page 9 · done</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>delivered - do NOT re-record</t>
+          <t>page 9 · h1</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
         </is>
       </c>
       <c r="G57" s="4" t="n">
-        <v>38</v>
+        <v>76</v>
       </c>
     </row>
     <row r="58">
@@ -2514,22 +2514,22 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_h1</t>
+          <t>vo_p7_h2</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_h1.wav</t>
+          <t>vo_p7_h2.wav</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>फिर से सुनिए। जिन शब्दों की शुरुआत ‘च’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
+          <t>जिन शब्दों की शुरुआत ‘च’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>page 9 · h1</t>
+          <t>page 9 · h2</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="G58" s="4" t="n">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59">
@@ -2547,22 +2547,22 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_h2</t>
+          <t>vo_p7_h3</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_h2.wav</t>
+          <t>vo_p7_h3.wav</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>जिन शब्दों की शुरुआत ‘च’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
+          <t>देखिए, ‘चाँद’ और ‘चश्मा’ की शुरुआत ‘च’ की आवाज़ से होती है। इन पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>page 9 · h2</t>
+          <t>page 9 · h3</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="G59" s="4" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
     </row>
     <row r="60">
@@ -2580,31 +2580,31 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_h3</t>
+          <t>vo_p7_hint</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_h3.wav</t>
+          <t>vo_p7_hint.wav</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>देखिए, ‘चाँद’ और ‘चश्मा’ की शुरुआत ‘च’ की आवाज़ से होती है। इन पर टैप कीजिए।</t>
+          <t>च की आवाज़ शुरू में भी हो सकती है और बीच में भी। पूरा शब्द सुनो।</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>page 9 · h3</t>
-        </is>
-      </c>
-      <c r="F60" s="6" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+          <t>page 9 · hint</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G60" s="4" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="61">
@@ -2613,22 +2613,22 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_hint</t>
+          <t>vo_p7_more</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_hint.wav</t>
+          <t>vo_p7_more.wav</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>च की आवाज़ शुरू में भी हो सकती है और बीच में भी। पूरा शब्द सुनो।</t>
+          <t>एक और च वाले शब्द पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>page 9 · hint</t>
+          <t>page 9 · more</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="G61" s="4" t="n">
-        <v>64</v>
+        <v>31</v>
       </c>
     </row>
     <row r="62">
@@ -2646,31 +2646,31 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_more</t>
+          <t>vo_p7_prompt</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_more.wav</t>
+          <t>vo_p7_prompt.wav</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>एक और च वाले शब्द पर टैप कीजिए।</t>
+          <t>“च” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>page 9 · more</t>
+          <t>page 9 · prompt</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>delivered - do NOT re-record</t>
+          <t>RE-RECORD - build differs from the delivered take</t>
         </is>
       </c>
       <c r="G62" s="4" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="63">
@@ -2679,31 +2679,31 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_prompt</t>
+          <t>vo_p7_reveal</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_prompt.wav</t>
+          <t>vo_p7_reveal.wav</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>“च” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
+          <t>सुनो — इसमें च की आवाज़ है।</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>page 9 · prompt</t>
+          <t>page 9 · reveal</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G63" s="4" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="64">
@@ -2712,22 +2712,22 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_reveal</t>
+          <t>vo_p7_try</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_reveal.wav</t>
+          <t>vo_p7_try.wav</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>सुनो — इसमें च की आवाज़ है।</t>
+          <t>इस शब्द में च की आवाज़ कहीं नहीं है। एक बार फिर सुनो।</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>page 9 · reveal</t>
+          <t>page 9 · try_again</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="G64" s="4" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
     </row>
     <row r="65">
@@ -2745,31 +2745,31 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_try</t>
+          <t>vo_p8_prompt</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_try.wav</t>
+          <t>vo_p8_prompt.wav</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>इस शब्द में च की आवाज़ कहीं नहीं है। एक बार फिर सुनो।</t>
+          <t>शाबाश! आज हमने सीखा — वाक्य ध्यान से सुनना, बार-बार आने वाली आवाज़ पहचानना, और प, च और म की आवाज़ ढूँढना।</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>page 9 · try_again</t>
+          <t>page 14 · prompt</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>delivered - do NOT re-record</t>
+          <t>RE-RECORD - build differs from the delivered take</t>
         </is>
       </c>
       <c r="G65" s="4" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
     </row>
     <row r="66">
@@ -2778,31 +2778,31 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>vo_p8_prompt</t>
+          <t>vo_snd_ch</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>vo_p8_prompt.wav</t>
+          <t>vo_snd_ch.wav</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>शाबाश! आज हमने सीखा — वाक्य ध्यान से सुनना, बार-बार आने वाली आवाज़ पहचानना, और प, च और म की आवाज़ ढूँढना।</t>
+          <t>च से चम्मच।</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>page 14 · prompt</t>
+          <t>page 2 · sound; page 9 · target</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
+          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
         </is>
       </c>
       <c r="G66" s="4" t="n">
-        <v>105</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67">
@@ -2811,31 +2811,31 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>vo_snd_ch</t>
+          <t>vo_snd_m</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>vo_snd_ch.wav</t>
+          <t>vo_snd_m.wav</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>च से चम्मच।</t>
+          <t>म से मछली।</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>page 2 · sound; page 9 · target</t>
+          <t>page 4 · sound; page 8 · target</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G67" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68">
@@ -2844,22 +2844,22 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>vo_snd_m</t>
+          <t>vo_snd_p</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>vo_snd_m.wav</t>
+          <t>vo_snd_p.wav</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>म से मछली।</t>
+          <t>प से पतंग।</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>page 4 · sound; page 8 · target</t>
+          <t>page 6 · sound; page 7 · target; page 12 · target; page 12 · target (2nd half) (+1 more)</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -2877,22 +2877,22 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>vo_snd_p</t>
+          <t>vo_t1_explain</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>vo_snd_p.wav</t>
+          <t>vo_t1_explain.wav</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>प से पतंग।</t>
+          <t>पीतल, पतीले, पपीता, पीला-पीला—इन सब शब्दों में प की आवाज़ बार-बार आई।</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>page 6 · sound; page 7 · target; page 12 · target; page 12 · target (2nd half) (+1 more)</t>
+          <t>page 5 · teach step 4</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="G69" s="4" t="n">
-        <v>10</v>
+        <v>69</v>
       </c>
     </row>
     <row r="70">
@@ -2910,22 +2910,22 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>vo_t1_explain</t>
+          <t>vo_t2_prompt</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>vo_t1_explain.wav</t>
+          <t>vo_t2_prompt.wav</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>पीतल, पतीले, पपीता, पीला-पीला—इन सब शब्दों में प की आवाज़ बार-बार आई।</t>
+          <t>हमने प की आवाज़ सुनी। यह आवाज़ प अक्षर से लिखी जाती है। जैसे—प से पपीता।</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>page 5 · teach step 4</t>
+          <t>page 6 · prompt</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -2934,7 +2934,7 @@
         </is>
       </c>
       <c r="G70" s="4" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="71">
@@ -2943,22 +2943,22 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>vo_t2_prompt</t>
+          <t>vo_t3_explain</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>vo_t2_prompt.wav</t>
+          <t>vo_t3_explain.wav</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>हमने प की आवाज़ सुनी। यह आवाज़ प अक्षर से लिखी जाती है। जैसे—प से पपीता।</t>
+          <t>चूहे, चार, चने, चबाए—इन सब शब्दों में च की आवाज़ बार-बार आई।</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>page 6 · prompt</t>
+          <t>page 1 · teach step 4</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="G71" s="4" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
     </row>
     <row r="72">
@@ -2976,22 +2976,22 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>vo_t3_explain</t>
+          <t>vo_t4_prompt</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>vo_t3_explain.wav</t>
+          <t>vo_t4_prompt.wav</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>चूहे, चार, चने, चबाए—इन सब शब्दों में च की आवाज़ बार-बार आई।</t>
+          <t>हमने च की आवाज़ सुनी। यह आवाज़ च अक्षर से लिखी जाती है। जैसे—च से चूहा।</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>page 1 · teach step 4</t>
+          <t>page 2 · prompt</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="G72" s="4" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="73">
@@ -3009,22 +3009,22 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>vo_t4_prompt</t>
+          <t>vo_t5_explain</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>vo_t4_prompt.wav</t>
+          <t>vo_t5_explain.wav</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>हमने च की आवाज़ सुनी। यह आवाज़ च अक्षर से लिखी जाती है। जैसे—च से चूहा।</t>
+          <t>मेरे, मामा, मीठी, मलाई—इन सब शब्दों में म की आवाज़ बार-बार आई।</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>page 2 · prompt</t>
+          <t>page 3 · teach step 4</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="G73" s="4" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="74">
@@ -3042,22 +3042,22 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>vo_t5_explain</t>
+          <t>vo_t6_prompt</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>vo_t5_explain.wav</t>
+          <t>vo_t6_prompt.wav</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>मेरे, मामा, मीठी, मलाई—इन सब शब्दों में म की आवाज़ बार-बार आई।</t>
+          <t>हमने म की आवाज़ सुनी। यह आवाज़ म अक्षर से लिखी जाती है। जैसे—म से मूली।</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>page 3 · teach step 4</t>
+          <t>page 4 · prompt</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="G74" s="4" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="75">
@@ -3075,22 +3075,22 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>vo_t6_prompt</t>
+          <t>vo_w_aam</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>vo_t6_prompt.wav</t>
+          <t>vo_w_aam.wav</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>हमने म की आवाज़ सुनी। यह आवाज़ म अक्षर से लिखी जाती है। जैसे—म से मूली।</t>
+          <t>आम</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>page 4 · prompt</t>
+          <t>page 7 · picture आम; page 13 · round 1 balloon आम; page 13 · round 2 refill आम</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="G75" s="4" t="n">
-        <v>71</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -3108,22 +3108,22 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>vo_w_aam</t>
+          <t>vo_w_chammach</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>vo_w_aam.wav</t>
+          <t>vo_w_chammach.wav</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>आम</t>
+          <t>चम्मच</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>page 7 · picture आम; page 13 · round 1 balloon आम; page 13 · round 2 refill आम</t>
+          <t>page 12 · picture चम्मच (2nd half); page 13 · round 2 balloon चम्मच</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="G76" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
@@ -3141,22 +3141,22 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chammach</t>
+          <t>vo_w_chand</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chammach.wav</t>
+          <t>vo_w_chand.wav</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>चम्मच</t>
+          <t>चाँद</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>page 12 · picture चम्मच (2nd half); page 13 · round 2 balloon चम्मच</t>
+          <t>page 9 · picture चाँद; page 12 · picture चाँद; page 13 · round 2 balloon चाँद</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="G77" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
@@ -3174,22 +3174,22 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chand</t>
+          <t>vo_w_chashma</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chand.wav</t>
+          <t>vo_w_chashma.wav</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>चाँद</t>
+          <t>चश्मा</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>page 9 · picture चाँद; page 12 · picture चाँद; page 13 · round 2 balloon चाँद</t>
+          <t>page 9 · picture चश्मा</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -3198,7 +3198,7 @@
         </is>
       </c>
       <c r="G78" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
@@ -3207,22 +3207,22 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chashma</t>
+          <t>vo_w_chidiya</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chashma.wav</t>
+          <t>vo_w_chidiya.wav</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>चश्मा</t>
+          <t>चिड़िया</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>page 9 · picture चश्मा</t>
+          <t>page 8 · picture चिड़िया</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="G79" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80">
@@ -3240,22 +3240,22 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chidiya</t>
+          <t>vo_w_chinti</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chidiya.wav</t>
+          <t>vo_w_chinti.wav</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>चिड़िया</t>
+          <t>चींटी</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>page 8 · picture चिड़िया</t>
+          <t>page 13 · round 2 balloon चींटी</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="G80" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
@@ -3273,22 +3273,22 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chinti</t>
+          <t>vo_w_chuha</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chinti.wav</t>
+          <t>vo_w_chuha.wav</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>चींटी</t>
+          <t>चूहा</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>page 13 · round 2 balloon चींटी</t>
+          <t>page 2 · word_name; page 12 · picture चूहा (2nd half); page 13 · round 2 balloon चूहा</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="G81" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chuha</t>
+          <t>vo_w_ghar</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chuha.wav</t>
+          <t>vo_w_ghar.wav</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>चूहा</t>
+          <t>घर</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>page 2 · word_name; page 12 · picture चूहा (2nd half); page 13 · round 2 balloon चूहा</t>
+          <t>page 13 · round 1 balloon घर; page 13 · round 2 refill घर</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="G82" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -3339,22 +3339,22 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>vo_w_ghar</t>
+          <t>vo_w_kabutar</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>vo_w_ghar.wav</t>
+          <t>vo_w_kabutar.wav</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>घर</t>
+          <t>कबूतर</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>page 13 · round 1 balloon घर; page 13 · round 2 refill घर</t>
+          <t>page 13 · round 2 balloon कबूतर</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="G83" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
@@ -3372,31 +3372,31 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kabutar</t>
+          <t>vo_w_kamal</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kabutar.wav</t>
+          <t>vo_w_kamal.wav</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>कबूतर</t>
+          <t>कमल</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>page 13 · round 2 balloon कबूतर</t>
+          <t>page 13 · round 2 balloon कमल</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>delivered - do NOT re-record</t>
+          <t>RE-RECORD - build differs from the delivered take</t>
         </is>
       </c>
       <c r="G84" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -3405,27 +3405,27 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kamal</t>
+          <t>vo_w_kauaa</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kamal.wav</t>
+          <t>vo_w_kauaa.wav</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>कमल</t>
+          <t>कौआ</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>page 13 · round 2 balloon कमल</t>
+          <t>page 13 · round 2 balloon कौआ</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G85" s="4" t="n">
@@ -3438,22 +3438,22 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kauaa</t>
+          <t>vo_w_kela</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kauaa.wav</t>
+          <t>vo_w_kela.wav</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>कौआ</t>
+          <t>केला</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>page 13 · round 2 balloon कौआ</t>
+          <t>page 7 · picture केला; page 13 · round 1 balloon केला; page 13 · round 2 balloon केला</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -3462,7 +3462,7 @@
         </is>
       </c>
       <c r="G86" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kela</t>
+          <t>vo_w_laal</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kela.wav</t>
+          <t>vo_w_laal.wav</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>केला</t>
+          <t>लाल</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>page 7 · picture केला; page 13 · round 1 balloon केला; page 13 · round 2 balloon केला</t>
+          <t>page 9 · picture लाल; page 13 · round 1 refill लाल</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="G87" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
@@ -3504,22 +3504,22 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>vo_w_laal</t>
+          <t>vo_w_laddu</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>vo_w_laal.wav</t>
+          <t>vo_w_laddu.wav</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>लाल</t>
+          <t>लड्डू</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>page 9 · picture लाल; page 13 · round 1 refill लाल</t>
+          <t>page 8 · picture लड्डू</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="G88" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
@@ -3537,22 +3537,22 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>vo_w_laddu</t>
+          <t>vo_w_machhli</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>vo_w_laddu.wav</t>
+          <t>vo_w_machhli.wav</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>लड्डू</t>
+          <t>मछली</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>page 8 · picture लड्डू</t>
+          <t>page 13 · round 1 balloon मछली; page 13 · round 2 refill मछली</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="G89" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
@@ -3570,22 +3570,22 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>vo_w_machhli</t>
+          <t>vo_w_mala</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>vo_w_machhli.wav</t>
+          <t>vo_w_mala.wav</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>मछली</t>
+          <t>माला</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>page 13 · round 1 balloon मछली; page 13 · round 2 refill मछली</t>
+          <t>page 9 · picture माला; page 13 · round 1 refill माला</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
@@ -3603,22 +3603,22 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>vo_w_mala</t>
+          <t>vo_w_mama</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>vo_w_mala.wav</t>
+          <t>vo_w_mama.wav</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>माला</t>
+          <t>मामा</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>page 9 · picture माला; page 13 · round 1 refill माला</t>
+          <t>page 8 · picture मामा</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -3636,22 +3636,22 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>vo_w_mama</t>
+          <t>vo_w_muli</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>vo_w_mama.wav</t>
+          <t>vo_w_muli.wav</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>मामा</t>
+          <t>मूली</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>page 8 · picture मामा</t>
+          <t>page 4 · word_name; page 8 · picture मूली; page 13 · round 1 refill मूली</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
@@ -3669,22 +3669,22 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>vo_w_muli</t>
+          <t>vo_w_pani</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>vo_w_muli.wav</t>
+          <t>vo_w_pani.wav</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>मूली</t>
+          <t>पानी</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>page 4 · word_name; page 8 · picture मूली; page 13 · round 1 refill मूली</t>
+          <t>page 12 · picture पानी (2nd half); page 13 · round 1 balloon पानी</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
@@ -3702,22 +3702,22 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>vo_w_pani</t>
+          <t>vo_w_papita</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>vo_w_pani.wav</t>
+          <t>vo_w_papita.wav</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>पानी</t>
+          <t>पपीता</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>page 12 · picture पानी (2nd half); page 13 · round 1 balloon पानी</t>
+          <t>page 6 · word_name; page 7 · picture पपीता; page 13 · round 1 balloon पपीता</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="G94" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95">
@@ -3735,22 +3735,22 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>vo_w_papita</t>
+          <t>vo_w_patang</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>vo_w_papita.wav</t>
+          <t>vo_w_patang.wav</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>पपीता</t>
+          <t>पतंग</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>page 6 · word_name; page 7 · picture पपीता; page 13 · round 1 balloon पपीता</t>
+          <t>page 7 · picture पतंग; page 12 · picture पतंग; page 13 · round 1 balloon पतंग</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="G95" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96">
@@ -3768,22 +3768,22 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>vo_w_patang</t>
+          <t>vo_w_patta</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>vo_w_patang.wav</t>
+          <t>vo_w_patta.wav</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>पतंग</t>
+          <t>पत्ता</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>page 7 · picture पतंग; page 12 · picture पतंग; page 13 · round 1 balloon पतंग</t>
+          <t>page 13 · round 1 balloon पत्ता</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="G96" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97">
@@ -3801,22 +3801,22 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>vo_w_patta</t>
+          <t>vo_w_payal</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>vo_w_patta.wav</t>
+          <t>vo_w_payal.wav</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>पत्ता</t>
+          <t>पायल</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>page 13 · round 1 balloon पत्ता</t>
+          <t>page 12 · picture पायल (2nd half)</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
@@ -3825,39 +3825,6 @@
         </is>
       </c>
       <c r="G97" s="4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="4" t="n">
-        <v>97</v>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>vo_w_payal</t>
-        </is>
-      </c>
-      <c r="C98" s="4" t="inlineStr">
-        <is>
-          <t>vo_w_payal.wav</t>
-        </is>
-      </c>
-      <c r="D98" s="5" t="inlineStr">
-        <is>
-          <t>पायल</t>
-        </is>
-      </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>page 12 · picture पायल (2nd half)</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>delivered - do NOT re-record</t>
-        </is>
-      </c>
-      <c r="G98" s="4" t="n">
         <v>4</v>
       </c>
     </row>

--- a/build/assets/Audio/audio_manifest.xlsx
+++ b/build/assets/Audio/audio_manifest.xlsx
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D2" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E2" t="n">
         <v>16</v>
@@ -611,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>page 10 · prompt</t>
+          <t>page 10 · prompt; page 11 · prompt</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -2349,22 +2349,22 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_prompt</t>
+          <t>vo_p4_reveal</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_prompt.wav</t>
+          <t>vo_p4_reveal.wav</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>कौन-सी आवाज़ शब्दों की शुरुआत में बार-बार आई?</t>
+          <t>शुरुआत में न की आवाज़ बार-बार आई।</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>page 11 · prompt</t>
+          <t>page 11 · reveal</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="G53" s="4" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="54">
@@ -2382,22 +2382,22 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_reveal</t>
+          <t>vo_p4_try</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_reveal.wav</t>
+          <t>vo_p4_try.wav</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>शुरुआत में न की आवाज़ बार-बार आई।</t>
+          <t>तुमने आखिरी आवाज़ सुनी। हमें वह आवाज़ ढूँढनी है जो पूरे वाक्य में बार-बार आई है।</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>page 11 · reveal</t>
+          <t>page 11 · try_again</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="G54" s="4" t="n">
-        <v>33</v>
+        <v>80</v>
       </c>
     </row>
     <row r="55">
@@ -2415,22 +2415,22 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_try</t>
+          <t>vo_p7_done</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_try.wav</t>
+          <t>vo_p7_done.wav</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>तुमने आखिरी आवाज़ सुनी। हमें वह आवाज़ ढूँढनी है जो पूरे वाक्य में बार-बार आई है।</t>
+          <t>वाह! तुमने च की आवाज़ हर जगह पहचान ली।</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>page 11 · try_again</t>
+          <t>page 9 · done</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="G55" s="4" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
     </row>
     <row r="56">
@@ -2448,31 +2448,31 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_done</t>
+          <t>vo_p7_h1</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_done.wav</t>
+          <t>vo_p7_h1.wav</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>वाह! तुमने च की आवाज़ हर जगह पहचान ली।</t>
+          <t>फिर से सुनिए। जिन शब्दों की शुरुआत ‘च’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>page 9 · done</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>delivered - do NOT re-record</t>
+          <t>page 9 · h1</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
         </is>
       </c>
       <c r="G56" s="4" t="n">
-        <v>38</v>
+        <v>76</v>
       </c>
     </row>
     <row r="57">
@@ -2481,22 +2481,22 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_h1</t>
+          <t>vo_p7_h2</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_h1.wav</t>
+          <t>vo_p7_h2.wav</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>फिर से सुनिए। जिन शब्दों की शुरुआत ‘च’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
+          <t>जिन शब्दों की शुरुआत ‘च’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>page 9 · h1</t>
+          <t>page 9 · h2</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="G57" s="4" t="n">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="58">
@@ -2514,22 +2514,22 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_h2</t>
+          <t>vo_p7_h3</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_h2.wav</t>
+          <t>vo_p7_h3.wav</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>जिन शब्दों की शुरुआत ‘च’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
+          <t>देखिए, ‘चाँद’ और ‘चश्मा’ की शुरुआत ‘च’ की आवाज़ से होती है। इन पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>page 9 · h2</t>
+          <t>page 9 · h3</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="G58" s="4" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
     </row>
     <row r="59">
@@ -2547,31 +2547,31 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_h3</t>
+          <t>vo_p7_hint</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_h3.wav</t>
+          <t>vo_p7_hint.wav</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>देखिए, ‘चाँद’ और ‘चश्मा’ की शुरुआत ‘च’ की आवाज़ से होती है। इन पर टैप कीजिए।</t>
+          <t>च की आवाज़ शुरू में भी हो सकती है और बीच में भी। पूरा शब्द सुनो।</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>page 9 · h3</t>
-        </is>
-      </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+          <t>page 9 · hint</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G59" s="4" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="60">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_hint</t>
+          <t>vo_p7_more</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_hint.wav</t>
+          <t>vo_p7_more.wav</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>च की आवाज़ शुरू में भी हो सकती है और बीच में भी। पूरा शब्द सुनो।</t>
+          <t>एक और च वाले शब्द पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>page 9 · hint</t>
+          <t>page 9 · more</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="G60" s="4" t="n">
-        <v>64</v>
+        <v>31</v>
       </c>
     </row>
     <row r="61">
@@ -2613,31 +2613,31 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_more</t>
+          <t>vo_p7_prompt</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_more.wav</t>
+          <t>vo_p7_prompt.wav</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>एक और च वाले शब्द पर टैप कीजिए।</t>
+          <t>“च” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>page 9 · more</t>
+          <t>page 9 · prompt</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>delivered - do NOT re-record</t>
+          <t>RE-RECORD - build differs from the delivered take</t>
         </is>
       </c>
       <c r="G61" s="4" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="62">
@@ -2646,31 +2646,31 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_prompt</t>
+          <t>vo_p7_reveal</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_prompt.wav</t>
+          <t>vo_p7_reveal.wav</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>“च” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
+          <t>सुनो — इसमें च की आवाज़ है।</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>page 9 · prompt</t>
+          <t>page 9 · reveal</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G62" s="4" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="63">
@@ -2679,22 +2679,22 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_reveal</t>
+          <t>vo_p7_try</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_reveal.wav</t>
+          <t>vo_p7_try.wav</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>सुनो — इसमें च की आवाज़ है।</t>
+          <t>इस शब्द में च की आवाज़ कहीं नहीं है। एक बार फिर सुनो।</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>page 9 · reveal</t>
+          <t>page 9 · try_again</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="G63" s="4" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64">
@@ -2712,31 +2712,31 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_try</t>
+          <t>vo_p8_prompt</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_try.wav</t>
+          <t>vo_p8_prompt.wav</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>इस शब्द में च की आवाज़ कहीं नहीं है। एक बार फिर सुनो।</t>
+          <t>शाबाश! आज हमने सीखा — वाक्य ध्यान से सुनना, बार-बार आने वाली आवाज़ पहचानना, और प, च और म की आवाज़ ढूँढना।</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>page 9 · try_again</t>
+          <t>page 14 · prompt</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>delivered - do NOT re-record</t>
+          <t>RE-RECORD - build differs from the delivered take</t>
         </is>
       </c>
       <c r="G64" s="4" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
     </row>
     <row r="65">
@@ -2745,31 +2745,31 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>vo_p8_prompt</t>
+          <t>vo_snd_ch</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>vo_p8_prompt.wav</t>
+          <t>vo_snd_ch.wav</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>शाबाश! आज हमने सीखा — वाक्य ध्यान से सुनना, बार-बार आने वाली आवाज़ पहचानना, और प, च और म की आवाज़ ढूँढना।</t>
+          <t>च से चम्मच।</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>page 14 · prompt</t>
+          <t>page 2 · sound; page 9 · target</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
+          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
         </is>
       </c>
       <c r="G65" s="4" t="n">
-        <v>105</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66">
@@ -2778,31 +2778,31 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>vo_snd_ch</t>
+          <t>vo_snd_m</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>vo_snd_ch.wav</t>
+          <t>vo_snd_m.wav</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>च से चम्मच।</t>
+          <t>म से मछली।</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>page 2 · sound; page 9 · target</t>
+          <t>page 4 · sound; page 8 · target</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G66" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67">
@@ -2811,22 +2811,22 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>vo_snd_m</t>
+          <t>vo_snd_p</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>vo_snd_m.wav</t>
+          <t>vo_snd_p.wav</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>म से मछली।</t>
+          <t>प से पतंग।</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>page 4 · sound; page 8 · target</t>
+          <t>page 6 · sound; page 7 · target; page 12 · target; page 12 · target (2nd half) (+1 more)</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -2844,22 +2844,22 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>vo_snd_p</t>
+          <t>vo_t1_explain</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>vo_snd_p.wav</t>
+          <t>vo_t1_explain.wav</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>प से पतंग।</t>
+          <t>पीतल, पतीले, पपीता, पीला-पीला—इन सब शब्दों में प की आवाज़ बार-बार आई।</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>page 6 · sound; page 7 · target; page 12 · target; page 12 · target (2nd half) (+1 more)</t>
+          <t>page 5 · teach step 4</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="G68" s="4" t="n">
-        <v>10</v>
+        <v>69</v>
       </c>
     </row>
     <row r="69">
@@ -2877,22 +2877,22 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>vo_t1_explain</t>
+          <t>vo_t2_prompt</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>vo_t1_explain.wav</t>
+          <t>vo_t2_prompt.wav</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>पीतल, पतीले, पपीता, पीला-पीला—इन सब शब्दों में प की आवाज़ बार-बार आई।</t>
+          <t>हमने प की आवाज़ सुनी। यह आवाज़ प अक्षर से लिखी जाती है। जैसे—प से पपीता।</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>page 5 · teach step 4</t>
+          <t>page 6 · prompt</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="G69" s="4" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70">
@@ -2910,22 +2910,22 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>vo_t2_prompt</t>
+          <t>vo_t3_explain</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>vo_t2_prompt.wav</t>
+          <t>vo_t3_explain.wav</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>हमने प की आवाज़ सुनी। यह आवाज़ प अक्षर से लिखी जाती है। जैसे—प से पपीता।</t>
+          <t>चूहे, चार, चने, चबाए—इन सब शब्दों में च की आवाज़ बार-बार आई।</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>page 6 · prompt</t>
+          <t>page 1 · teach step 4</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -2934,7 +2934,7 @@
         </is>
       </c>
       <c r="G70" s="4" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
     </row>
     <row r="71">
@@ -2943,22 +2943,22 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>vo_t3_explain</t>
+          <t>vo_t4_prompt</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>vo_t3_explain.wav</t>
+          <t>vo_t4_prompt.wav</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>चूहे, चार, चने, चबाए—इन सब शब्दों में च की आवाज़ बार-बार आई।</t>
+          <t>हमने च की आवाज़ सुनी। यह आवाज़ च अक्षर से लिखी जाती है। जैसे—च से चूहा।</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>page 1 · teach step 4</t>
+          <t>page 2 · prompt</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="G71" s="4" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="72">
@@ -2976,22 +2976,22 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>vo_t4_prompt</t>
+          <t>vo_t5_explain</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>vo_t4_prompt.wav</t>
+          <t>vo_t5_explain.wav</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>हमने च की आवाज़ सुनी। यह आवाज़ च अक्षर से लिखी जाती है। जैसे—च से चूहा।</t>
+          <t>मेरे, मामा, मीठी, मलाई—इन सब शब्दों में म की आवाज़ बार-बार आई।</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>page 2 · prompt</t>
+          <t>page 3 · teach step 4</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="G72" s="4" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="73">
@@ -3009,22 +3009,22 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>vo_t5_explain</t>
+          <t>vo_t6_prompt</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>vo_t5_explain.wav</t>
+          <t>vo_t6_prompt.wav</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>मेरे, मामा, मीठी, मलाई—इन सब शब्दों में म की आवाज़ बार-बार आई।</t>
+          <t>हमने म की आवाज़ सुनी। यह आवाज़ म अक्षर से लिखी जाती है। जैसे—म से मूली।</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>page 3 · teach step 4</t>
+          <t>page 4 · prompt</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="G73" s="4" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="74">
@@ -3042,22 +3042,22 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>vo_t6_prompt</t>
+          <t>vo_w_aam</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>vo_t6_prompt.wav</t>
+          <t>vo_w_aam.wav</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>हमने म की आवाज़ सुनी। यह आवाज़ म अक्षर से लिखी जाती है। जैसे—म से मूली।</t>
+          <t>आम</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>page 4 · prompt</t>
+          <t>page 7 · picture आम; page 13 · round 1 balloon आम; page 13 · round 2 refill आम</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="G74" s="4" t="n">
-        <v>71</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -3075,22 +3075,22 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>vo_w_aam</t>
+          <t>vo_w_chammach</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>vo_w_aam.wav</t>
+          <t>vo_w_chammach.wav</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>आम</t>
+          <t>चम्मच</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>page 7 · picture आम; page 13 · round 1 balloon आम; page 13 · round 2 refill आम</t>
+          <t>page 12 · picture चम्मच (2nd half); page 13 · round 2 balloon चम्मच</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="G75" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76">
@@ -3108,22 +3108,22 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chammach</t>
+          <t>vo_w_chand</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chammach.wav</t>
+          <t>vo_w_chand.wav</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>चम्मच</t>
+          <t>चाँद</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>page 12 · picture चम्मच (2nd half); page 13 · round 2 balloon चम्मच</t>
+          <t>page 9 · picture चाँद; page 12 · picture चाँद; page 13 · round 2 balloon चाँद</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="G76" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
@@ -3141,22 +3141,22 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chand</t>
+          <t>vo_w_chashma</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chand.wav</t>
+          <t>vo_w_chashma.wav</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>चाँद</t>
+          <t>चश्मा</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>page 9 · picture चाँद; page 12 · picture चाँद; page 13 · round 2 balloon चाँद</t>
+          <t>page 9 · picture चश्मा</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="G77" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
@@ -3174,22 +3174,22 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chashma</t>
+          <t>vo_w_chidiya</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chashma.wav</t>
+          <t>vo_w_chidiya.wav</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>चश्मा</t>
+          <t>चिड़िया</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>page 9 · picture चश्मा</t>
+          <t>page 8 · picture चिड़िया</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -3198,7 +3198,7 @@
         </is>
       </c>
       <c r="G78" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
@@ -3207,22 +3207,22 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chidiya</t>
+          <t>vo_w_chinti</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chidiya.wav</t>
+          <t>vo_w_chinti.wav</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>चिड़िया</t>
+          <t>चींटी</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>page 8 · picture चिड़िया</t>
+          <t>page 13 · round 2 balloon चींटी</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="G79" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
@@ -3240,22 +3240,22 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chinti</t>
+          <t>vo_w_chuha</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chinti.wav</t>
+          <t>vo_w_chuha.wav</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>चींटी</t>
+          <t>चूहा</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>page 13 · round 2 balloon चींटी</t>
+          <t>page 2 · word_name; page 12 · picture चूहा (2nd half); page 13 · round 2 balloon चूहा</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="G80" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
@@ -3273,22 +3273,22 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chuha</t>
+          <t>vo_w_ghar</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chuha.wav</t>
+          <t>vo_w_ghar.wav</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>चूहा</t>
+          <t>घर</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>page 2 · word_name; page 12 · picture चूहा (2nd half); page 13 · round 2 balloon चूहा</t>
+          <t>page 13 · round 1 balloon घर; page 13 · round 2 refill घर</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="G81" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>vo_w_ghar</t>
+          <t>vo_w_kabutar</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>vo_w_ghar.wav</t>
+          <t>vo_w_kabutar.wav</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>घर</t>
+          <t>कबूतर</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>page 13 · round 1 balloon घर; page 13 · round 2 refill घर</t>
+          <t>page 13 · round 2 balloon कबूतर</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="G82" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -3339,31 +3339,31 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kabutar</t>
+          <t>vo_w_kamal</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kabutar.wav</t>
+          <t>vo_w_kamal.wav</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>कबूतर</t>
+          <t>कमल</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>page 13 · round 2 balloon कबूतर</t>
+          <t>page 13 · round 2 balloon कमल</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>delivered - do NOT re-record</t>
+          <t>RE-RECORD - build differs from the delivered take</t>
         </is>
       </c>
       <c r="G83" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -3372,27 +3372,27 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kamal</t>
+          <t>vo_w_kauaa</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kamal.wav</t>
+          <t>vo_w_kauaa.wav</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>कमल</t>
+          <t>कौआ</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>page 13 · round 2 balloon कमल</t>
+          <t>page 13 · round 2 balloon कौआ</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G84" s="4" t="n">
@@ -3405,22 +3405,22 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kauaa</t>
+          <t>vo_w_kela</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kauaa.wav</t>
+          <t>vo_w_kela.wav</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>कौआ</t>
+          <t>केला</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>page 13 · round 2 balloon कौआ</t>
+          <t>page 7 · picture केला; page 13 · round 1 balloon केला; page 13 · round 2 balloon केला</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -3429,7 +3429,7 @@
         </is>
       </c>
       <c r="G85" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
@@ -3438,22 +3438,22 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kela</t>
+          <t>vo_w_laal</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kela.wav</t>
+          <t>vo_w_laal.wav</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>केला</t>
+          <t>लाल</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>page 7 · picture केला; page 13 · round 1 balloon केला; page 13 · round 2 balloon केला</t>
+          <t>page 9 · picture लाल; page 13 · round 1 refill लाल</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -3462,7 +3462,7 @@
         </is>
       </c>
       <c r="G86" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>vo_w_laal</t>
+          <t>vo_w_laddu</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>vo_w_laal.wav</t>
+          <t>vo_w_laddu.wav</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>लाल</t>
+          <t>लड्डू</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>page 9 · picture लाल; page 13 · round 1 refill लाल</t>
+          <t>page 8 · picture लड्डू</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="G87" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88">
@@ -3504,22 +3504,22 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>vo_w_laddu</t>
+          <t>vo_w_machhli</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>vo_w_laddu.wav</t>
+          <t>vo_w_machhli.wav</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>लड्डू</t>
+          <t>मछली</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>page 8 · picture लड्डू</t>
+          <t>page 13 · round 1 balloon मछली; page 13 · round 2 refill मछली</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="G88" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
@@ -3537,22 +3537,22 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>vo_w_machhli</t>
+          <t>vo_w_mala</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>vo_w_machhli.wav</t>
+          <t>vo_w_mala.wav</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>मछली</t>
+          <t>माला</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>page 13 · round 1 balloon मछली; page 13 · round 2 refill मछली</t>
+          <t>page 9 · picture माला; page 13 · round 1 refill माला</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -3570,22 +3570,22 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>vo_w_mala</t>
+          <t>vo_w_mama</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>vo_w_mala.wav</t>
+          <t>vo_w_mama.wav</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>माला</t>
+          <t>मामा</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>page 9 · picture माला; page 13 · round 1 refill माला</t>
+          <t>page 8 · picture मामा</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
@@ -3603,22 +3603,22 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>vo_w_mama</t>
+          <t>vo_w_muli</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>vo_w_mama.wav</t>
+          <t>vo_w_muli.wav</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>मामा</t>
+          <t>मूली</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>page 8 · picture मामा</t>
+          <t>page 4 · word_name; page 8 · picture मूली; page 13 · round 1 refill मूली</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -3636,22 +3636,22 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>vo_w_muli</t>
+          <t>vo_w_pani</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>vo_w_muli.wav</t>
+          <t>vo_w_pani.wav</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>मूली</t>
+          <t>पानी</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>page 4 · word_name; page 8 · picture मूली; page 13 · round 1 refill मूली</t>
+          <t>page 12 · picture पानी (2nd half); page 13 · round 1 balloon पानी</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
@@ -3669,22 +3669,22 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>vo_w_pani</t>
+          <t>vo_w_papita</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>vo_w_pani.wav</t>
+          <t>vo_w_papita.wav</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>पानी</t>
+          <t>पपीता</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>page 12 · picture पानी (2nd half); page 13 · round 1 balloon पानी</t>
+          <t>page 6 · word_name; page 7 · picture पपीता; page 13 · round 1 balloon पपीता</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="G93" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
@@ -3702,22 +3702,22 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>vo_w_papita</t>
+          <t>vo_w_patang</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>vo_w_papita.wav</t>
+          <t>vo_w_patang.wav</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>पपीता</t>
+          <t>पतंग</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>page 6 · word_name; page 7 · picture पपीता; page 13 · round 1 balloon पपीता</t>
+          <t>page 7 · picture पतंग; page 12 · picture पतंग; page 13 · round 1 balloon पतंग</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="G94" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95">
@@ -3735,22 +3735,22 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>vo_w_patang</t>
+          <t>vo_w_patta</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>vo_w_patang.wav</t>
+          <t>vo_w_patta.wav</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>पतंग</t>
+          <t>पत्ता</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>page 7 · picture पतंग; page 12 · picture पतंग; page 13 · round 1 balloon पतंग</t>
+          <t>page 13 · round 1 balloon पत्ता</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="G95" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
@@ -3768,22 +3768,22 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>vo_w_patta</t>
+          <t>vo_w_payal</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>vo_w_patta.wav</t>
+          <t>vo_w_payal.wav</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>पत्ता</t>
+          <t>पायल</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>page 13 · round 1 balloon पत्ता</t>
+          <t>page 12 · picture पायल (2nd half)</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
@@ -3792,39 +3792,6 @@
         </is>
       </c>
       <c r="G96" s="4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>vo_w_payal</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>vo_w_payal.wav</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="inlineStr">
-        <is>
-          <t>पायल</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>page 12 · picture पायल (2nd half)</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>delivered - do NOT re-record</t>
-        </is>
-      </c>
-      <c r="G97" s="4" t="n">
         <v>4</v>
       </c>
     </row>

--- a/build/assets/Audio/audio_manifest.xlsx
+++ b/build/assets/Audio/audio_manifest.xlsx
@@ -1237,7 +1237,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>फिर से सुनिए। वाक्य ध्यान से सुनिए और देखिए कौन-सी आवाज़ बार-बार आ रही है।</t>
+          <t>फिर से पढ़िए।</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="G19" s="4" t="n">
-        <v>74</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>फिर से सुनिए। वाक्य ध्यान से सुनिए और देखिए शब्दों की शुरुआत में कौन-सी आवाज़ बार-बार आ रही है।</t>
+          <t>फिर से पढ़िए।</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -2274,7 +2274,7 @@
         </is>
       </c>
       <c r="G50" s="4" t="n">
-        <v>95</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51">

--- a/build/assets/Audio/audio_manifest.xlsx
+++ b/build/assets/Audio/audio_manifest.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HI02H11_L01_S01" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TO RECORD" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HI02H11_L01_S01" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,8 +51,12 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Nirmala UI"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +71,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -95,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,6 +116,16 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -472,6 +492,778 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="66" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>VO ID</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Deliver as (exact filename)</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Hindi line (speak exactly this)</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Heard on</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Why it is on this list</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Chars</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>vo_g2_h1</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>vo_g2_h1.wav</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>फिर से सुनिए। जिन शब्दों की शुरुआत ‘प’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>page 7 · h1</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>vo_g2_h2</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>vo_g2_h2.wav</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>जिन शब्दों की शुरुआत ‘प’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>page 7 · h2</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>vo_g2_h3</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>vo_g2_h3.wav</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>देखिए, ‘पपीता’ और ‘पतंग’ की शुरुआत ‘प’ की आवाज़ से होती है। इन पर टैप कीजिए।</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>page 7 · h3</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>vo_g3_h1</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>vo_g3_h1.wav</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>फिर से पढ़िए।</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>page 10 · h1</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>vo_g3_h3</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>vo_g3_h3.wav</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>चूहे, चार, चने, चबाए… इन सबमें ‘च’ की आवाज़ है। ‘च’ पर टैप कीजिए।</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>page 10 · h3</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>vo_g5_h1</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>vo_g5_h1.wav</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>फिर से सुनिए। चित्र का नाम ध्यान से सुनिए और देखिए उसकी शुरुआत किस आवाज़ से होती है।</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>page 12 · h1 (2nd half)</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>vo_p1_h1</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>vo_p1_h1.wav</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>फिर से सुनिए। जिन शब्दों की शुरुआत ‘म’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>page 8 · h1</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>vo_p1_h2</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>vo_p1_h2.wav</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>जिन शब्दों की शुरुआत ‘म’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>page 8 · h2</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>vo_p1_h3</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>vo_p1_h3.wav</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>देखिए, ‘मामा’ और ‘मूली’ की शुरुआत ‘म’ की आवाज़ से होती है। इन पर टैप कीजिए।</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>page 8 · h3</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>vo_p4_h1</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>vo_p4_h1.wav</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>फिर से पढ़िए।</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>page 11 · h1</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>vo_p4_h3</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>vo_p4_h3.wav</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>नानी, ने, नई, नाव… इन सबकी शुरुआत ‘न’ की आवाज़ से होती है। ‘न’ पर टैप कीजिए।</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>page 11 · h3</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>vo_p7_h1</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>vo_p7_h1.wav</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>फिर से सुनिए। जिन शब्दों की शुरुआत ‘च’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>page 9 · h1</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>vo_p7_h2</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>vo_p7_h2.wav</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>जिन शब्दों की शुरुआत ‘च’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>page 9 · h2</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>vo_p7_h3</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>vo_p7_h3.wav</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>देखिए, ‘चाँद’ और ‘चश्मा’ की शुरुआत ‘च’ की आवाज़ से होती है। इन पर टैप कीजिए।</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>page 9 · h3</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>vo_landing</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>vo_landing.wav</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>नमस्ते दोस्तो! आज हम जानेंगे वाक्य में बार-बार आने वाली ध्वनि यानी आवाज़ के बारे में।</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>cover · narration</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SYNTHESISED - record a human take of the line in column D</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>vo_g2_prompt</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>vo_g2_prompt.wav</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>“प” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>page 7 · prompt</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>RE-RECORD - build differs from the delivered take</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>vo_p1_prompt</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>vo_p1_prompt.wav</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>“म” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>page 8 · prompt</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>RE-RECORD - build differs from the delivered take</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>vo_p7_prompt</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>vo_p7_prompt.wav</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>“च” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>page 9 · prompt</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>RE-RECORD - build differs from the delivered take</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>vo_p8_prompt</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>vo_p8_prompt.wav</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>शाबाश! आज हमने सीखा — वाक्य ध्यान से सुनना, बार-बार आने वाली आवाज़ पहचानना, और प, च और म की आवाज़ ढूँढना।</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>page 14 · prompt</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>RE-RECORD - build differs from the delivered take  |  AFTER this take lands: re-run _assets_round4/make_lipsync.py. The end screen's lip-sync is measured from THIS clip; a new take without it leaves her mouth running to the old rhythm.</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>vo_w_kamal</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>vo_w_kamal.wav</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>कमल</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>page 13 · round 2 balloon कमल</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>RE-RECORD - build differs from the delivered take</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>20 line(s) to record. Highlighted rows are new takes - nothing can play them until they arrive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>AUDIO FORMAT - please deliver exactly this:</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WAV, 16-bit PCM, MONO, 48 kHz.  One file per row, named as column C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    16-bit WAV is a hard requirement, not a preference: the word-by-word highlighting is timed by</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    reading the waveform, and that reader only understands 16-bit PCM WAV.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    No added silence, no fades, no music bed, no brickwall normalisation - a clean room take.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Send the folder as-is; the build renames and encodes (Opus 28k mono) on its own.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -521,13 +1313,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D2" t="n">
         <v>79</v>
       </c>
       <c r="E2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -559,42 +1351,42 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    WAV, 16-bit PCM, MONO, 48 kHz.  One file per row, named as column C (e.g. vo_landing.wav).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    16-bit WAV is a hard requirement, not a preference: the word-by-word highlighting is timed by</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    reading the waveform, and that reader only understands 16-bit PCM WAV. An MP3/OGG/M4A delivery</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    still plays, but the highlighting silently falls back to guessed timing and drifts out of sync.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    No added silence, no fades, no music bed, no normalisation to a brickwall - a clean room take.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Send the folder as-is; the build renames and encodes (Opus 28k mono) on its own.</t>
         </is>
@@ -605,13 +1397,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1260,22 +2052,22 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>vo_g3_h2</t>
+          <t>vo_g3_h3</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>vo_g3_h2.wav</t>
+          <t>vo_g3_h3.wav</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>सुनिए, कौन-सी आवाज़ बार-बार आ रही है? उसी अक्षर पर टैप कीजिए।</t>
+          <t>चूहे, चार, चने, चबाए… इन सबमें ‘च’ की आवाज़ है। ‘च’ पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>page 10 · h2</t>
+          <t>page 10 · h3</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -1284,7 +2076,7 @@
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21">
@@ -1293,31 +2085,31 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>vo_g3_h3</t>
+          <t>vo_g3_prompt</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>vo_g3_h3.wav</t>
+          <t>vo_g3_prompt.wav</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>चूहे, चार, चने, चबाए… इन सबमें ‘च’ की आवाज़ है। ‘च’ पर टैप कीजिए।</t>
+          <t>इस वाक्य में कौन-सी आवाज़ बार-बार आई?</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>page 10 · h3</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+          <t>page 10 · prompt; page 11 · prompt</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G21" s="4" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22">
@@ -1326,22 +2118,22 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>vo_g3_prompt</t>
+          <t>vo_g3_reveal</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>vo_g3_prompt.wav</t>
+          <t>vo_g3_reveal.wav</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>इस वाक्य में कौन-सी आवाज़ बार-बार आई?</t>
+          <t>ध्यान से देखिए, सही जवाब च है।</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>page 10 · prompt; page 11 · prompt</t>
+          <t>page 10 · reveal</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1350,7 +2142,7 @@
         </is>
       </c>
       <c r="G22" s="4" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
@@ -1359,22 +2151,22 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>vo_g3_reveal</t>
+          <t>vo_g3_try</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>vo_g3_reveal.wav</t>
+          <t>vo_g3_try.wav</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>ध्यान से देखिए, सही जवाब च है।</t>
+          <t>यह च की आवाज़ नहीं है।</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>page 10 · reveal</t>
+          <t>page 10 · try_again</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1383,7 +2175,7 @@
         </is>
       </c>
       <c r="G23" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24">
@@ -1392,22 +2184,22 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>vo_g3_try</t>
+          <t>vo_g5_correct</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>vo_g3_try.wav</t>
+          <t>vo_g5_correct.wav</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>यह च की आवाज़ नहीं है।</t>
+          <t>बहुत बढ़िया! सही डिब्बा।</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>page 10 · try_again</t>
+          <t>page 12 · correct; page 12 · correct (2nd half)</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1416,7 +2208,7 @@
         </is>
       </c>
       <c r="G24" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25">
@@ -1425,31 +2217,31 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>vo_g5_correct</t>
+          <t>vo_g5_h1</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>vo_g5_correct.wav</t>
+          <t>vo_g5_h1.wav</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>बहुत बढ़िया! सही डिब्बा।</t>
+          <t>फिर से सुनिए। चित्र का नाम ध्यान से सुनिए और देखिए उसकी शुरुआत किस आवाज़ से होती है।</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>page 12 · correct; page 12 · correct (2nd half)</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>delivered - do NOT re-record</t>
+          <t>page 12 · h1 (2nd half)</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
         </is>
       </c>
       <c r="G25" s="4" t="n">
-        <v>24</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26">
@@ -1458,31 +2250,31 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>vo_g5_h1</t>
+          <t>vo_g5_hint</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>vo_g5_h1.wav</t>
+          <t>vo_g5_hint.wav</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>फिर से सुनिए। चित्र का नाम ध्यान से सुनिए और देखिए उसकी शुरुआत किस आवाज़ से होती है।</t>
+          <t>शब्द बोलो और सुनो — उसमें प की आवाज़ है या च की?</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>page 12 · h1 (2nd half)</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+          <t>page 12 · hint (2nd half)</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G26" s="4" t="n">
-        <v>84</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27">
@@ -1491,22 +2283,22 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>vo_g5_hint</t>
+          <t>vo_g5_prompt</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>vo_g5_hint.wav</t>
+          <t>vo_g5_prompt.wav</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>शब्द बोलो और सुनो — उसमें प की आवाज़ है या च की?</t>
+          <t>हर चित्र का नाम सुनिए और उसे सही डिब्बे में डालिए।</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>page 12 · hint (2nd half)</t>
+          <t>page 12 · prompt; page 12 · prompt (2nd half)</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1515,7 +2307,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28">
@@ -1524,22 +2316,22 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>vo_g5_prompt</t>
+          <t>vo_g5_try</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>vo_g5_prompt.wav</t>
+          <t>vo_g5_try.wav</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>हर चित्र का नाम सुनिए और उसे सही डिब्बे में डालिए।</t>
+          <t>यह डिब्बा सही नहीं है। शब्द की आवाज़ फिर सुनो।</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>page 12 · prompt; page 12 · prompt (2nd half)</t>
+          <t>page 12 · try_again (2nd half)</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1548,7 +2340,7 @@
         </is>
       </c>
       <c r="G28" s="4" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29">
@@ -1557,22 +2349,22 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>vo_g5_try</t>
+          <t>vo_line_l1</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>vo_g5_try.wav</t>
+          <t>vo_line_l1.wav</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>यह डिब्बा सही नहीं है। शब्द की आवाज़ फिर सुनो।</t>
+          <t>पीतल के पतीले में पपीता पीला-पीला।</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>page 12 · try_again (2nd half)</t>
+          <t>page 5 · prompt; page 5 · whole line</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1581,7 +2373,7 @@
         </is>
       </c>
       <c r="G29" s="4" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30">
@@ -1590,22 +2382,22 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>vo_line_l1</t>
+          <t>vo_line_l2</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>vo_line_l1.wav</t>
+          <t>vo_line_l2.wav</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>पीतल के पतीले में पपीता पीला-पीला।</t>
+          <t>चूहे ने चार चने चबाए।</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>page 5 · prompt; page 5 · whole line</t>
+          <t>page 1 · prompt; page 1 · whole line; page 10 · whole line</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1614,7 +2406,7 @@
         </is>
       </c>
       <c r="G30" s="4" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31">
@@ -1623,22 +2415,22 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>vo_line_l2</t>
+          <t>vo_line_l3</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>vo_line_l2.wav</t>
+          <t>vo_line_l3.wav</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>चूहे ने चार चने चबाए।</t>
+          <t>मेरे मामा मीठी मलाई लाए।</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>page 1 · prompt; page 1 · whole line; page 10 · whole line</t>
+          <t>page 3 · prompt; page 3 · whole line</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1647,7 +2439,7 @@
         </is>
       </c>
       <c r="G31" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32">
@@ -1656,22 +2448,22 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>vo_line_l3</t>
+          <t>vo_line_l6</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>vo_line_l3.wav</t>
+          <t>vo_line_l6.wav</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>मेरे मामा मीठी मलाई लाए।</t>
+          <t>नानी ने नई नाव बनाई।</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>page 3 · prompt; page 3 · whole line</t>
+          <t>page 11 · whole line</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1680,7 +2472,7 @@
         </is>
       </c>
       <c r="G32" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
@@ -1689,31 +2481,31 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>vo_line_l6</t>
+          <t>vo_ltr_ch</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>vo_line_l6.wav</t>
+          <t>vo_ltr_ch.wav</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>नानी ने नई नाव बनाई।</t>
+          <t>च</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>page 11 · whole line</t>
+          <t>page 1 · target; page 1 · option च; page 10 · target; page 10 · option च</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>delivered - do NOT re-record</t>
+          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
         </is>
       </c>
       <c r="G33" s="4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1722,22 +2514,22 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_ch</t>
+          <t>vo_ltr_l</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_ch.wav</t>
+          <t>vo_ltr_l.wav</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>च</t>
+          <t>ल</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>page 1 · target; page 1 · option च; page 10 · target; page 10 · option च</t>
+          <t>page 10 · option ल; page 11 · option ल</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -1755,22 +2547,22 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_l</t>
+          <t>vo_ltr_m</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_l.wav</t>
+          <t>vo_ltr_m.wav</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>ल</t>
+          <t>म</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>page 10 · option ल; page 11 · option ल</t>
+          <t>page 3 · target; page 3 · option म; page 11 · option म</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -1788,22 +2580,22 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_m</t>
+          <t>vo_ltr_n</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_m.wav</t>
+          <t>vo_ltr_n.wav</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>म</t>
+          <t>न</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>page 3 · target; page 3 · option म; page 11 · option म</t>
+          <t>page 11 · target; page 11 · option न</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -1821,22 +2613,22 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_n</t>
+          <t>vo_ltr_p</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_n.wav</t>
+          <t>vo_ltr_p.wav</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>न</t>
+          <t>प</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>page 11 · target; page 11 · option न</t>
+          <t>page 5 · target; page 5 · option प</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -1854,22 +2646,22 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_p</t>
+          <t>vo_ltr_r</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_p.wav</t>
+          <t>vo_ltr_r.wav</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>प</t>
+          <t>र</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>page 5 · target; page 5 · option प</t>
+          <t>page 10 · option र</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -1887,31 +2679,31 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_r</t>
+          <t>vo_p1_done</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>vo_ltr_r.wav</t>
+          <t>vo_p1_done.wav</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>र</t>
+          <t>शाबाश! म की आवाज़ वाले सारे शब्द मिल गए।</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>page 10 · option र</t>
+          <t>page 8 · done</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G39" s="4" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40">
@@ -1920,31 +2712,31 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_done</t>
+          <t>vo_p1_h1</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_done.wav</t>
+          <t>vo_p1_h1.wav</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>शाबाश! म की आवाज़ वाले सारे शब्द मिल गए।</t>
+          <t>फिर से सुनिए। जिन शब्दों की शुरुआत ‘म’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>page 8 · done</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>delivered - do NOT re-record</t>
+          <t>page 8 · h1</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
         </is>
       </c>
       <c r="G40" s="4" t="n">
-        <v>40</v>
+        <v>76</v>
       </c>
     </row>
     <row r="41">
@@ -1953,22 +2745,22 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_h1</t>
+          <t>vo_p1_h2</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_h1.wav</t>
+          <t>vo_p1_h2.wav</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>फिर से सुनिए। जिन शब्दों की शुरुआत ‘म’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
+          <t>जिन शब्दों की शुरुआत ‘म’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>page 8 · h1</t>
+          <t>page 8 · h2</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -1977,7 +2769,7 @@
         </is>
       </c>
       <c r="G41" s="4" t="n">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="42">
@@ -1986,22 +2778,22 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_h2</t>
+          <t>vo_p1_h3</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_h2.wav</t>
+          <t>vo_p1_h3.wav</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>जिन शब्दों की शुरुआत ‘म’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
+          <t>देखिए, ‘मामा’ और ‘मूली’ की शुरुआत ‘म’ की आवाज़ से होती है। इन पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>page 8 · h2</t>
+          <t>page 8 · h3</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -2010,7 +2802,7 @@
         </is>
       </c>
       <c r="G42" s="4" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
     </row>
     <row r="43">
@@ -2019,31 +2811,31 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_h3</t>
+          <t>vo_p1_hint</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_h3.wav</t>
+          <t>vo_p1_hint.wav</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>देखिए, ‘मामा’ और ‘मूली’ की शुरुआत ‘म’ की आवाज़ से होती है। इन पर टैप कीजिए।</t>
+          <t>हर शब्द सुनो — क्या उसमें म की आवाज़ सुनाई देती है?</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>page 8 · h3</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+          <t>page 8 · hint</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G43" s="4" t="n">
-        <v>75</v>
+        <v>51</v>
       </c>
     </row>
     <row r="44">
@@ -2052,22 +2844,22 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_hint</t>
+          <t>vo_p1_more</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_hint.wav</t>
+          <t>vo_p1_more.wav</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>हर शब्द सुनो — क्या उसमें म की आवाज़ सुनाई देती है?</t>
+          <t>एक और म वाले शब्द पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>page 8 · hint</t>
+          <t>page 8 · more</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -2076,7 +2868,7 @@
         </is>
       </c>
       <c r="G44" s="4" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45">
@@ -2085,31 +2877,31 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_more</t>
+          <t>vo_p1_prompt</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_more.wav</t>
+          <t>vo_p1_prompt.wav</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>एक और म वाले शब्द पर टैप कीजिए।</t>
+          <t>“म” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>page 8 · more</t>
+          <t>page 8 · prompt</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>delivered - do NOT re-record</t>
+          <t>RE-RECORD - build differs from the delivered take</t>
         </is>
       </c>
       <c r="G45" s="4" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46">
@@ -2118,31 +2910,31 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_prompt</t>
+          <t>vo_p1_reveal</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_prompt.wav</t>
+          <t>vo_p1_reveal.wav</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>“म” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
+          <t>सुनो — इसमें म की आवाज़ है।</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>page 8 · prompt</t>
+          <t>page 8 · reveal</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G46" s="4" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47">
@@ -2151,22 +2943,22 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_reveal</t>
+          <t>vo_p1_try</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_reveal.wav</t>
+          <t>vo_p1_try.wav</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>सुनो — इसमें म की आवाज़ है।</t>
+          <t>इस शब्द की शुरुआत में म की आवाज़ नहीं है। एक बार फिर सुनो।</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>page 8 · reveal</t>
+          <t>page 8 · try_again</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -2175,7 +2967,7 @@
         </is>
       </c>
       <c r="G47" s="4" t="n">
-        <v>27</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48">
@@ -2184,22 +2976,22 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_try</t>
+          <t>vo_p4_correct</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>vo_p1_try.wav</t>
+          <t>vo_p4_correct.wav</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>इस शब्द की शुरुआत में म की आवाज़ नहीं है। एक बार फिर सुनो।</t>
+          <t>सही! शुरुआत में न की आवाज़ थी।</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>page 8 · try_again</t>
+          <t>page 11 · correct</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -2208,7 +3000,7 @@
         </is>
       </c>
       <c r="G48" s="4" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49">
@@ -2217,31 +3009,31 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_correct</t>
+          <t>vo_p4_h1</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_correct.wav</t>
+          <t>vo_p4_h1.wav</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>सही! शुरुआत में न की आवाज़ थी।</t>
+          <t>फिर से पढ़िए।</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>page 11 · correct</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>delivered - do NOT re-record</t>
+          <t>page 11 · h1</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
         </is>
       </c>
       <c r="G49" s="4" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50">
@@ -2250,22 +3042,22 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_h1</t>
+          <t>vo_p4_h3</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_h1.wav</t>
+          <t>vo_p4_h3.wav</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>फिर से पढ़िए।</t>
+          <t>नानी, ने, नई, नाव… इन सबकी शुरुआत ‘न’ की आवाज़ से होती है। ‘न’ पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>page 11 · h1</t>
+          <t>page 11 · h3</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
@@ -2274,7 +3066,7 @@
         </is>
       </c>
       <c r="G50" s="4" t="n">
-        <v>13</v>
+        <v>76</v>
       </c>
     </row>
     <row r="51">
@@ -2283,31 +3075,31 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_h2</t>
+          <t>vo_p4_reveal</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_h2.wav</t>
+          <t>vo_p4_reveal.wav</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>सुनिए, कौन-सी आवाज़ बार-बार आ रही है? उसी अक्षर पर टैप कीजिए।</t>
+          <t>शुरुआत में न की आवाज़ बार-बार आई।</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>page 11 · h2</t>
-        </is>
-      </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+          <t>page 11 · reveal</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G51" s="4" t="n">
-        <v>61</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52">
@@ -2316,31 +3108,31 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_h3</t>
+          <t>vo_p4_try</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_h3.wav</t>
+          <t>vo_p4_try.wav</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>नानी, ने, नई, नाव… इन सबकी शुरुआत ‘न’ की आवाज़ से होती है। ‘न’ पर टैप कीजिए।</t>
+          <t>तुमने आखिरी आवाज़ सुनी। हमें वह आवाज़ ढूँढनी है जो पूरे वाक्य में बार-बार आई है।</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>page 11 · h3</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+          <t>page 11 · try_again</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G52" s="4" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="53">
@@ -2349,22 +3141,22 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_reveal</t>
+          <t>vo_p7_done</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_reveal.wav</t>
+          <t>vo_p7_done.wav</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>शुरुआत में न की आवाज़ बार-बार आई।</t>
+          <t>वाह! तुमने च की आवाज़ हर जगह पहचान ली।</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>page 11 · reveal</t>
+          <t>page 9 · done</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -2373,7 +3165,7 @@
         </is>
       </c>
       <c r="G53" s="4" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="54">
@@ -2382,31 +3174,31 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_try</t>
+          <t>vo_p7_h1</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>vo_p4_try.wav</t>
+          <t>vo_p7_h1.wav</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>तुमने आखिरी आवाज़ सुनी। हमें वह आवाज़ ढूँढनी है जो पूरे वाक्य में बार-बार आई है।</t>
+          <t>फिर से सुनिए। जिन शब्दों की शुरुआत ‘च’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>page 11 · try_again</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>delivered - do NOT re-record</t>
+          <t>page 9 · h1</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
         </is>
       </c>
       <c r="G54" s="4" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55">
@@ -2415,31 +3207,31 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_done</t>
+          <t>vo_p7_h2</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_done.wav</t>
+          <t>vo_p7_h2.wav</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>वाह! तुमने च की आवाज़ हर जगह पहचान ली।</t>
+          <t>जिन शब्दों की शुरुआत ‘च’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>page 9 · done</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>delivered - do NOT re-record</t>
+          <t>page 9 · h2</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>NOT RECORDED - new line, needs a first take</t>
         </is>
       </c>
       <c r="G55" s="4" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
     </row>
     <row r="56">
@@ -2448,22 +3240,22 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_h1</t>
+          <t>vo_p7_h3</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_h1.wav</t>
+          <t>vo_p7_h3.wav</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>फिर से सुनिए। जिन शब्दों की शुरुआत ‘च’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
+          <t>देखिए, ‘चाँद’ और ‘चश्मा’ की शुरुआत ‘च’ की आवाज़ से होती है। इन पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>page 9 · h1</t>
+          <t>page 9 · h3</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
@@ -2481,31 +3273,31 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_h2</t>
+          <t>vo_p7_hint</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_h2.wav</t>
+          <t>vo_p7_hint.wav</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>जिन शब्दों की शुरुआत ‘च’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
+          <t>च की आवाज़ शुरू में भी हो सकती है और बीच में भी। पूरा शब्द सुनो।</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>page 9 · h2</t>
-        </is>
-      </c>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+          <t>page 9 · hint</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G57" s="4" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="58">
@@ -2514,31 +3306,31 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_h3</t>
+          <t>vo_p7_more</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_h3.wav</t>
+          <t>vo_p7_more.wav</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>देखिए, ‘चाँद’ और ‘चश्मा’ की शुरुआत ‘च’ की आवाज़ से होती है। इन पर टैप कीजिए।</t>
+          <t>एक और च वाले शब्द पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>page 9 · h3</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
+          <t>page 9 · more</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G58" s="4" t="n">
-        <v>76</v>
+        <v>31</v>
       </c>
     </row>
     <row r="59">
@@ -2547,31 +3339,31 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_hint</t>
+          <t>vo_p7_prompt</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_hint.wav</t>
+          <t>vo_p7_prompt.wav</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>च की आवाज़ शुरू में भी हो सकती है और बीच में भी। पूरा शब्द सुनो।</t>
+          <t>“च” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>page 9 · hint</t>
+          <t>page 9 · prompt</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>delivered - do NOT re-record</t>
+          <t>RE-RECORD - build differs from the delivered take</t>
         </is>
       </c>
       <c r="G59" s="4" t="n">
-        <v>64</v>
+        <v>38</v>
       </c>
     </row>
     <row r="60">
@@ -2580,22 +3372,22 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_more</t>
+          <t>vo_p7_reveal</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_more.wav</t>
+          <t>vo_p7_reveal.wav</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>एक और च वाले शब्द पर टैप कीजिए।</t>
+          <t>सुनो — इसमें च की आवाज़ है।</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>page 9 · more</t>
+          <t>page 9 · reveal</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -2604,7 +3396,7 @@
         </is>
       </c>
       <c r="G60" s="4" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="61">
@@ -2613,31 +3405,31 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_prompt</t>
+          <t>vo_p7_try</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_prompt.wav</t>
+          <t>vo_p7_try.wav</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>“च” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
+          <t>इस शब्द में च की आवाज़ कहीं नहीं है। एक बार फिर सुनो।</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>page 9 · prompt</t>
+          <t>page 9 · try_again</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G61" s="4" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="62">
@@ -2646,31 +3438,31 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_reveal</t>
+          <t>vo_p8_prompt</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_reveal.wav</t>
+          <t>vo_p8_prompt.wav</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>सुनो — इसमें च की आवाज़ है।</t>
+          <t>शाबाश! आज हमने सीखा — वाक्य ध्यान से सुनना, बार-बार आने वाली आवाज़ पहचानना, और प, च और म की आवाज़ ढूँढना।</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>page 9 · reveal</t>
+          <t>page 14 · prompt</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>delivered - do NOT re-record</t>
+          <t>RE-RECORD - build differs from the delivered take</t>
         </is>
       </c>
       <c r="G62" s="4" t="n">
-        <v>27</v>
+        <v>105</v>
       </c>
     </row>
     <row r="63">
@@ -2679,31 +3471,31 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_try</t>
+          <t>vo_snd_ch</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>vo_p7_try.wav</t>
+          <t>vo_snd_ch.wav</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>इस शब्द में च की आवाज़ कहीं नहीं है। एक बार फिर सुनो।</t>
+          <t>च से चम्मच।</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>page 9 · try_again</t>
+          <t>page 2 · sound; page 9 · target</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>delivered - do NOT re-record</t>
+          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
         </is>
       </c>
       <c r="G63" s="4" t="n">
-        <v>53</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64">
@@ -2712,31 +3504,31 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>vo_p8_prompt</t>
+          <t>vo_snd_m</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>vo_p8_prompt.wav</t>
+          <t>vo_snd_m.wav</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>शाबाश! आज हमने सीखा — वाक्य ध्यान से सुनना, बार-बार आने वाली आवाज़ पहचानना, और प, च और म की आवाज़ ढूँढना।</t>
+          <t>म से मछली।</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>page 14 · prompt</t>
+          <t>page 4 · sound; page 8 · target</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G64" s="4" t="n">
-        <v>105</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65">
@@ -2745,31 +3537,31 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>vo_snd_ch</t>
+          <t>vo_snd_p</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>vo_snd_ch.wav</t>
+          <t>vo_snd_p.wav</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>च से चम्मच।</t>
+          <t>प से पतंग।</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>page 2 · sound; page 9 · target</t>
+          <t>page 6 · sound; page 7 · target; page 12 · target; page 12 · target (2nd half) (+1 more)</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G65" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66">
@@ -2778,22 +3570,22 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>vo_snd_m</t>
+          <t>vo_t1_explain</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>vo_snd_m.wav</t>
+          <t>vo_t1_explain.wav</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>म से मछली।</t>
+          <t>पीतल, पतीले, पपीता, पीला-पीला—इन सब शब्दों में प की आवाज़ बार-बार आई।</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>page 4 · sound; page 8 · target</t>
+          <t>page 5 · teach step 4</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -2802,7 +3594,7 @@
         </is>
       </c>
       <c r="G66" s="4" t="n">
-        <v>10</v>
+        <v>69</v>
       </c>
     </row>
     <row r="67">
@@ -2811,22 +3603,22 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>vo_snd_p</t>
+          <t>vo_t2_prompt</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>vo_snd_p.wav</t>
+          <t>vo_t2_prompt.wav</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>प से पतंग।</t>
+          <t>हमने प की आवाज़ सुनी। यह आवाज़ प अक्षर से लिखी जाती है। जैसे—प से पपीता।</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>page 6 · sound; page 7 · target; page 12 · target; page 12 · target (2nd half) (+1 more)</t>
+          <t>page 6 · prompt</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -2835,7 +3627,7 @@
         </is>
       </c>
       <c r="G67" s="4" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
     </row>
     <row r="68">
@@ -2844,22 +3636,22 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>vo_t1_explain</t>
+          <t>vo_t3_explain</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>vo_t1_explain.wav</t>
+          <t>vo_t3_explain.wav</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>पीतल, पतीले, पपीता, पीला-पीला—इन सब शब्दों में प की आवाज़ बार-बार आई।</t>
+          <t>चूहे, चार, चने, चबाए—इन सब शब्दों में च की आवाज़ बार-बार आई।</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>page 5 · teach step 4</t>
+          <t>page 1 · teach step 4</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -2868,7 +3660,7 @@
         </is>
       </c>
       <c r="G68" s="4" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="69">
@@ -2877,22 +3669,22 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>vo_t2_prompt</t>
+          <t>vo_t4_prompt</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>vo_t2_prompt.wav</t>
+          <t>vo_t4_prompt.wav</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>हमने प की आवाज़ सुनी। यह आवाज़ प अक्षर से लिखी जाती है। जैसे—प से पपीता।</t>
+          <t>हमने च की आवाज़ सुनी। यह आवाज़ च अक्षर से लिखी जाती है। जैसे—च से चूहा।</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>page 6 · prompt</t>
+          <t>page 2 · prompt</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -2901,7 +3693,7 @@
         </is>
       </c>
       <c r="G69" s="4" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="70">
@@ -2910,22 +3702,22 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>vo_t3_explain</t>
+          <t>vo_t5_explain</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>vo_t3_explain.wav</t>
+          <t>vo_t5_explain.wav</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>चूहे, चार, चने, चबाए—इन सब शब्दों में च की आवाज़ बार-बार आई।</t>
+          <t>मेरे, मामा, मीठी, मलाई—इन सब शब्दों में म की आवाज़ बार-बार आई।</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>page 1 · teach step 4</t>
+          <t>page 3 · teach step 4</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -2934,7 +3726,7 @@
         </is>
       </c>
       <c r="G70" s="4" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="71">
@@ -2943,22 +3735,22 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>vo_t4_prompt</t>
+          <t>vo_t6_prompt</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>vo_t4_prompt.wav</t>
+          <t>vo_t6_prompt.wav</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>हमने च की आवाज़ सुनी। यह आवाज़ च अक्षर से लिखी जाती है। जैसे—च से चूहा।</t>
+          <t>हमने म की आवाज़ सुनी। यह आवाज़ म अक्षर से लिखी जाती है। जैसे—म से मूली।</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>page 2 · prompt</t>
+          <t>page 4 · prompt</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -2976,22 +3768,22 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>vo_t5_explain</t>
+          <t>vo_w_aam</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>vo_t5_explain.wav</t>
+          <t>vo_w_aam.wav</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>मेरे, मामा, मीठी, मलाई—इन सब शब्दों में म की आवाज़ बार-बार आई।</t>
+          <t>आम</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>page 3 · teach step 4</t>
+          <t>page 7 · picture आम; page 13 · round 1 balloon आम; page 13 · round 2 refill आम</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -3000,7 +3792,7 @@
         </is>
       </c>
       <c r="G72" s="4" t="n">
-        <v>62</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -3009,22 +3801,22 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>vo_t6_prompt</t>
+          <t>vo_w_chammach</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>vo_t6_prompt.wav</t>
+          <t>vo_w_chammach.wav</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>हमने म की आवाज़ सुनी। यह आवाज़ म अक्षर से लिखी जाती है। जैसे—म से मूली।</t>
+          <t>चम्मच</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>page 4 · prompt</t>
+          <t>page 12 · picture चम्मच (2nd half); page 13 · round 2 balloon चम्मच</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -3033,7 +3825,7 @@
         </is>
       </c>
       <c r="G73" s="4" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -3042,22 +3834,22 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>vo_w_aam</t>
+          <t>vo_w_chand</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>vo_w_aam.wav</t>
+          <t>vo_w_chand.wav</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>आम</t>
+          <t>चाँद</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>page 7 · picture आम; page 13 · round 1 balloon आम; page 13 · round 2 refill आम</t>
+          <t>page 9 · picture चाँद; page 12 · picture चाँद; page 13 · round 2 balloon चाँद</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -3066,7 +3858,7 @@
         </is>
       </c>
       <c r="G74" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
@@ -3075,22 +3867,22 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chammach</t>
+          <t>vo_w_chashma</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chammach.wav</t>
+          <t>vo_w_chashma.wav</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>चम्मच</t>
+          <t>चश्मा</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>page 12 · picture चम्मच (2nd half); page 13 · round 2 balloon चम्मच</t>
+          <t>page 9 · picture चश्मा</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -3108,22 +3900,22 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chand</t>
+          <t>vo_w_chidiya</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chand.wav</t>
+          <t>vo_w_chidiya.wav</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>चाँद</t>
+          <t>चिड़िया</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>page 9 · picture चाँद; page 12 · picture चाँद; page 13 · round 2 balloon चाँद</t>
+          <t>page 8 · picture चिड़िया</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -3132,7 +3924,7 @@
         </is>
       </c>
       <c r="G76" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77">
@@ -3141,22 +3933,22 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chashma</t>
+          <t>vo_w_chinti</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chashma.wav</t>
+          <t>vo_w_chinti.wav</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>चश्मा</t>
+          <t>चींटी</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>page 9 · picture चश्मा</t>
+          <t>page 13 · round 2 balloon चींटी</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -3174,22 +3966,22 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chidiya</t>
+          <t>vo_w_chuha</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chidiya.wav</t>
+          <t>vo_w_chuha.wav</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>चिड़िया</t>
+          <t>चूहा</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>page 8 · picture चिड़िया</t>
+          <t>page 2 · word_name; page 12 · picture चूहा (2nd half); page 13 · round 2 balloon चूहा</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -3198,7 +3990,7 @@
         </is>
       </c>
       <c r="G78" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
@@ -3207,22 +3999,22 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chinti</t>
+          <t>vo_w_ghar</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chinti.wav</t>
+          <t>vo_w_ghar.wav</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>चींटी</t>
+          <t>घर</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>page 13 · round 2 balloon चींटी</t>
+          <t>page 13 · round 1 balloon घर; page 13 · round 2 refill घर</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -3231,7 +4023,7 @@
         </is>
       </c>
       <c r="G79" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -3240,22 +4032,22 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chuha</t>
+          <t>vo_w_kabutar</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>vo_w_chuha.wav</t>
+          <t>vo_w_kabutar.wav</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>चूहा</t>
+          <t>कबूतर</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>page 2 · word_name; page 12 · picture चूहा (2nd half); page 13 · round 2 balloon चूहा</t>
+          <t>page 13 · round 2 balloon कबूतर</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -3264,7 +4056,7 @@
         </is>
       </c>
       <c r="G80" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
@@ -3273,31 +4065,31 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>vo_w_ghar</t>
+          <t>vo_w_kamal</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>vo_w_ghar.wav</t>
+          <t>vo_w_kamal.wav</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>घर</t>
+          <t>कमल</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>page 13 · round 1 balloon घर; page 13 · round 2 refill घर</t>
+          <t>page 13 · round 2 balloon कमल</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>delivered - do NOT re-record</t>
+          <t>RE-RECORD - build differs from the delivered take</t>
         </is>
       </c>
       <c r="G81" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -3306,22 +4098,22 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kabutar</t>
+          <t>vo_w_kauaa</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kabutar.wav</t>
+          <t>vo_w_kauaa.wav</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>कबूतर</t>
+          <t>कौआ</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>page 13 · round 2 balloon कबूतर</t>
+          <t>page 13 · round 2 balloon कौआ</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -3330,7 +4122,7 @@
         </is>
       </c>
       <c r="G82" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -3339,31 +4131,31 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kamal</t>
+          <t>vo_w_kela</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kamal.wav</t>
+          <t>vo_w_kela.wav</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>कमल</t>
+          <t>केला</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>page 13 · round 2 balloon कमल</t>
+          <t>page 7 · picture केला; page 13 · round 1 balloon केला; page 13 · round 2 balloon केला</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="G83" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
@@ -3372,22 +4164,22 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kauaa</t>
+          <t>vo_w_laal</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kauaa.wav</t>
+          <t>vo_w_laal.wav</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>कौआ</t>
+          <t>लाल</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>page 13 · round 2 balloon कौआ</t>
+          <t>page 9 · picture लाल; page 13 · round 1 refill लाल</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -3405,22 +4197,22 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kela</t>
+          <t>vo_w_laddu</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>vo_w_kela.wav</t>
+          <t>vo_w_laddu.wav</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>केला</t>
+          <t>लड्डू</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>page 7 · picture केला; page 13 · round 1 balloon केला; page 13 · round 2 balloon केला</t>
+          <t>page 8 · picture लड्डू</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -3429,7 +4221,7 @@
         </is>
       </c>
       <c r="G85" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
@@ -3438,22 +4230,22 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>vo_w_laal</t>
+          <t>vo_w_machhli</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>vo_w_laal.wav</t>
+          <t>vo_w_machhli.wav</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>लाल</t>
+          <t>मछली</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>page 9 · picture लाल; page 13 · round 1 refill लाल</t>
+          <t>page 13 · round 1 balloon मछली; page 13 · round 2 refill मछली</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -3462,7 +4254,7 @@
         </is>
       </c>
       <c r="G86" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
@@ -3471,22 +4263,22 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>vo_w_laddu</t>
+          <t>vo_w_mala</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>vo_w_laddu.wav</t>
+          <t>vo_w_mala.wav</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>लड्डू</t>
+          <t>माला</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>page 8 · picture लड्डू</t>
+          <t>page 9 · picture माला; page 13 · round 1 refill माला</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -3495,7 +4287,7 @@
         </is>
       </c>
       <c r="G87" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
@@ -3504,22 +4296,22 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>vo_w_machhli</t>
+          <t>vo_w_mama</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>vo_w_machhli.wav</t>
+          <t>vo_w_mama.wav</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>मछली</t>
+          <t>मामा</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>page 13 · round 1 balloon मछली; page 13 · round 2 refill मछली</t>
+          <t>page 8 · picture मामा</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -3537,22 +4329,22 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>vo_w_mala</t>
+          <t>vo_w_muli</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>vo_w_mala.wav</t>
+          <t>vo_w_muli.wav</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>माला</t>
+          <t>मूली</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>page 9 · picture माला; page 13 · round 1 refill माला</t>
+          <t>page 4 · word_name; page 8 · picture मूली; page 13 · round 1 refill मूली</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -3570,22 +4362,22 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>vo_w_mama</t>
+          <t>vo_w_pani</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>vo_w_mama.wav</t>
+          <t>vo_w_pani.wav</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>मामा</t>
+          <t>पानी</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>page 8 · picture मामा</t>
+          <t>page 12 · picture पानी (2nd half); page 13 · round 1 balloon पानी</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
@@ -3603,22 +4395,22 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>vo_w_muli</t>
+          <t>vo_w_papita</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>vo_w_muli.wav</t>
+          <t>vo_w_papita.wav</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>मूली</t>
+          <t>पपीता</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>page 4 · word_name; page 8 · picture मूली; page 13 · round 1 refill मूली</t>
+          <t>page 6 · word_name; page 7 · picture पपीता; page 13 · round 1 balloon पपीता</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -3627,7 +4419,7 @@
         </is>
       </c>
       <c r="G91" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
@@ -3636,22 +4428,22 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>vo_w_pani</t>
+          <t>vo_w_patang</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>vo_w_pani.wav</t>
+          <t>vo_w_patang.wav</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>पानी</t>
+          <t>पतंग</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>page 12 · picture पानी (2nd half); page 13 · round 1 balloon पानी</t>
+          <t>page 7 · picture पतंग; page 12 · picture पतंग; page 13 · round 1 balloon पतंग</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
@@ -3669,22 +4461,22 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>vo_w_papita</t>
+          <t>vo_w_patta</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>vo_w_papita.wav</t>
+          <t>vo_w_patta.wav</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>पपीता</t>
+          <t>पत्ता</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>page 6 · word_name; page 7 · picture पपीता; page 13 · round 1 balloon पपीता</t>
+          <t>page 13 · round 1 balloon पत्ता</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
@@ -3702,22 +4494,22 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>vo_w_patang</t>
+          <t>vo_w_payal</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>vo_w_patang.wav</t>
+          <t>vo_w_payal.wav</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>पतंग</t>
+          <t>पायल</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>page 7 · picture पतंग; page 12 · picture पतंग; page 13 · round 1 balloon पतंग</t>
+          <t>page 12 · picture पायल (2nd half)</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
@@ -3726,72 +4518,6 @@
         </is>
       </c>
       <c r="G94" s="4" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="4" t="n">
-        <v>94</v>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>vo_w_patta</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>vo_w_patta.wav</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
-        <is>
-          <t>पत्ता</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>page 13 · round 1 balloon पत्ता</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>delivered - do NOT re-record</t>
-        </is>
-      </c>
-      <c r="G95" s="4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="4" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>vo_w_payal</t>
-        </is>
-      </c>
-      <c r="C96" s="4" t="inlineStr">
-        <is>
-          <t>vo_w_payal.wav</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="inlineStr">
-        <is>
-          <t>पायल</t>
-        </is>
-      </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>page 12 · picture पायल (2nd half)</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>delivered - do NOT re-record</t>
-        </is>
-      </c>
-      <c r="G96" s="4" t="n">
         <v>4</v>
       </c>
     </row>

--- a/build/assets/Audio/audio_manifest.xlsx
+++ b/build/assets/Audio/audio_manifest.xlsx
@@ -56,7 +56,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -66,16 +66,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3B70"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -105,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -114,19 +104,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -492,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -506,810 +488,94 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Page</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>VO ID</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Deliver as (exact filename)</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Hindi line (speak exactly this)</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Heard on</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Why it is on this list</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Chars</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>cover</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>vo_landing</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>vo_landing.wav</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>नमस्ते दोस्तो! आज हम जानेंगे वाक्य में बार-बार आने वाली ध्वनि यानी आवाज़ के बारे में।</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>cover · narration</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>SYNTHESISED - record a human take of the line in column D</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>85</v>
-      </c>
-    </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>page 7</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>vo_g2_prompt</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>vo_g2_prompt.wav</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>“प” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>page 7 · prompt</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>38</v>
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>0 line(s) to record. Highlighted rows are new takes - nothing can play them until they arrive.</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="9" t="inlineStr"/>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>vo_g2_h1</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>vo_g2_h1.wav</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>फिर से सुनिए। जिन शब्दों की शुरुआत ‘प’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>page 7 · h1</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="n">
-        <v>76</v>
-      </c>
+      <c r="A4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="9" t="inlineStr"/>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>vo_g2_h2</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>vo_g2_h2.wav</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>जिन शब्दों की शुरुआत ‘प’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>page 7 · h2</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>62</v>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>AUDIO FORMAT - please deliver exactly this:</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="9" t="inlineStr"/>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>vo_g2_h3</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>vo_g2_h3.wav</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>देखिए, ‘पपीता’ और ‘पतंग’ की शुरुआत ‘प’ की आवाज़ से होती है। इन पर टैप कीजिए।</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>page 7 · h3</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="n">
-        <v>76</v>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WAV, 16-bit PCM, MONO, 48 kHz.  One file per row, named as column C.</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>page 8</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>vo_p1_prompt</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>vo_p1_prompt.wav</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>“म” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>page 8 · prompt</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>38</v>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    16-bit WAV is a hard requirement, not a preference: the word-by-word highlighting is timed by</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="9" t="inlineStr"/>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>vo_p1_h1</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>vo_p1_h1.wav</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>फिर से सुनिए। जिन शब्दों की शुरुआत ‘म’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>page 8 · h1</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-      <c r="H8" s="9" t="n">
-        <v>76</v>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    reading the waveform, and that reader only understands 16-bit PCM WAV.</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="9" t="inlineStr"/>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>vo_p1_h2</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>vo_p1_h2.wav</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>जिन शब्दों की शुरुआत ‘म’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>page 8 · h2</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="n">
-        <v>62</v>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    No added silence, no fades, no music bed, no brickwall normalisation - a clean room take.</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="9" t="inlineStr"/>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>vo_p1_h3</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>vo_p1_h3.wav</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>देखिए, ‘मामा’ और ‘मूली’ की शुरुआत ‘म’ की आवाज़ से होती है। इन पर टैप कीजिए।</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>page 8 · h3</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>page 9</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>vo_p7_prompt</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>vo_p7_prompt.wav</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>“च” की आवाज़ वाले शब्दों पर टैप कीजिए।</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>page 9 · prompt</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="9" t="inlineStr"/>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>vo_p7_h1</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>vo_p7_h1.wav</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>फिर से सुनिए। जिन शब्दों की शुरुआत ‘च’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>page 9 · h1</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-      <c r="H12" s="9" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="9" t="inlineStr"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>vo_p7_h2</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>vo_p7_h2.wav</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>जिन शब्दों की शुरुआत ‘च’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>page 9 · h2</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-      <c r="H13" s="9" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="9" t="inlineStr"/>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>vo_p7_h3</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>vo_p7_h3.wav</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>देखिए, ‘चाँद’ और ‘चश्मा’ की शुरुआत ‘च’ की आवाज़ से होती है। इन पर टैप कीजिए।</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>page 9 · h3</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>page 10</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>vo_g3_h1</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>vo_g3_h1.wav</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>फिर से पढ़िए।</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>page 10 · h1</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="9" t="inlineStr"/>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>vo_g3_h3</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>vo_g3_h3.wav</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>चूहे, चार, चने, चबाए… इन सबमें ‘च’ की आवाज़ है। ‘च’ पर टैप कीजिए।</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>page 10 · h3</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-      <c r="H16" s="9" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>page 11</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>vo_p4_h1</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>vo_p4_h1.wav</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>फिर से पढ़िए।</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>page 11 · h1</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="9" t="inlineStr"/>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>vo_p4_h3</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>vo_p4_h3.wav</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>नानी, ने, नई, नाव… इन सबकी शुरुआत ‘न’ की आवाज़ से होती है। ‘न’ पर टैप कीजिए।</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>page 11 · h3</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-      <c r="H18" s="9" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>page 12</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>vo_g5_h1</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>vo_g5_h1.wav</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>फिर से सुनिए। चित्र का नाम ध्यान से सुनिए और देखिए उसकी शुरुआत किस आवाज़ से होती है।</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>page 12 · h1 (2nd half)</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-      <c r="H19" s="9" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>page 13</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>vo_w_kamal</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>vo_w_kamal.wav</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>कमल</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>page 13 · round 2 balloon कमल</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>page 14</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>vo_p8_prompt</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>vo_p8_prompt.wav</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>शाबाश! आज हमने सीखा — वाक्य ध्यान से सुनना, बार-बार आने वाली आवाज़ पहचानना, और प, च और म की आवाज़ ढूँढना।</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>page 14 · prompt</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>RE-RECORD - build differs from the delivered take  |  AFTER this take lands: re-run _assets_round4/make_lipsync.py. The end screen's lip-sync is measured from THIS clip; a new take without it leaves her mouth running to the old rhythm.</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>20 line(s) to record. Highlighted rows are new takes - nothing can play them until they arrive.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>AUDIO FORMAT - please deliver exactly this:</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    WAV, 16-bit PCM, MONO, 48 kHz.  One file per row, named as column C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    16-bit WAV is a hard requirement, not a preference: the word-by-word highlighting is timed by</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    reading the waveform, and that reader only understands 16-bit PCM WAV.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    No added silence, no fades, no music bed, no brickwall normalisation - a clean room take.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">    Send the folder as-is; the build renames and encodes (Opus 28k mono) on its own.</t>
         </is>
@@ -1378,10 +644,10 @@
         <v>93</v>
       </c>
       <c r="D2" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1406,49 +672,49 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>AUDIO FORMAT - please deliver exactly this:</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">    WAV, 16-bit PCM, MONO, 48 kHz.  One file per row, named as column C (e.g. vo_landing.wav).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">    16-bit WAV is a hard requirement, not a preference: the word-by-word highlighting is timed by</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">    reading the waveform, and that reader only understands 16-bit PCM WAV. An MP3/OGG/M4A delivery</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">    still plays, but the highlighting silently falls back to guessed timing and drifts out of sync.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">    No added silence, no fades, no music bed, no normalisation to a brickwall - a clean room take.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">    Send the folder as-is; the build renames and encodes (Opus 28k mono) on its own.</t>
         </is>
@@ -1479,42 +745,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Page</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>VO ID</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Deliver as (exact filename)</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Hindi line (speak exactly this)</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Heard on</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Chars</t>
         </is>
@@ -1551,7 +817,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SYNTHESISED - record a human take of the line in column D</t>
+          <t>delivered - build holds a deliberate TRIM; do NOT re-record</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -2225,7 +1491,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -2471,104 +1737,104 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="n">
+      <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="9" t="inlineStr"/>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
         <is>
           <t>vo_g2_h1</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>vo_g2_h1.wav</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>फिर से सुनिए। जिन शब्दों की शुरुआत ‘प’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="F29" s="9" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>page 7 · h1</t>
         </is>
       </c>
-      <c r="G29" s="9" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-      <c r="H29" s="9" t="n">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
         <v>76</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="n">
+      <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="9" t="inlineStr"/>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
         <is>
           <t>vo_g2_h2</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>vo_g2_h2.wav</t>
         </is>
       </c>
-      <c r="E30" s="10" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>जिन शब्दों की शुरुआत ‘प’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="F30" s="9" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>page 7 · h2</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-      <c r="H30" s="9" t="n">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
         <v>62</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="n">
+      <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="9" t="inlineStr"/>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
         <is>
           <t>vo_g2_h3</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>vo_g2_h3.wav</t>
         </is>
       </c>
-      <c r="E31" s="10" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>देखिए, ‘पपीता’ और ‘पतंग’ की शुरुआत ‘प’ की आवाज़ से होती है। इन पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>page 7 · h3</t>
         </is>
       </c>
-      <c r="G31" s="9" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-      <c r="H31" s="9" t="n">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
         <v>76</v>
       </c>
     </row>
@@ -2637,7 +1903,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -2883,104 +2149,104 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="n">
+      <c r="A41" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="9" t="inlineStr"/>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
         <is>
           <t>vo_p1_h1</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>vo_p1_h1.wav</t>
         </is>
       </c>
-      <c r="E41" s="10" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>फिर से सुनिए। जिन शब्दों की शुरुआत ‘म’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>page 8 · h1</t>
         </is>
       </c>
-      <c r="G41" s="9" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-      <c r="H41" s="9" t="n">
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
         <v>76</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="n">
+      <c r="A42" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="9" t="inlineStr"/>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
         <is>
           <t>vo_p1_h2</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>vo_p1_h2.wav</t>
         </is>
       </c>
-      <c r="E42" s="10" t="inlineStr">
+      <c r="E42" s="8" t="inlineStr">
         <is>
           <t>जिन शब्दों की शुरुआत ‘म’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="F42" s="9" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>page 8 · h2</t>
         </is>
       </c>
-      <c r="G42" s="9" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-      <c r="H42" s="9" t="n">
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
         <v>62</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="n">
+      <c r="A43" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="9" t="inlineStr"/>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
         <is>
           <t>vo_p1_h3</t>
         </is>
       </c>
-      <c r="D43" s="9" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>vo_p1_h3.wav</t>
         </is>
       </c>
-      <c r="E43" s="10" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr">
         <is>
           <t>देखिए, ‘मामा’ और ‘मूली’ की शुरुआत ‘म’ की आवाज़ से होती है। इन पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="F43" s="9" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>page 8 · h3</t>
         </is>
       </c>
-      <c r="G43" s="9" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-      <c r="H43" s="9" t="n">
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
         <v>75</v>
       </c>
     </row>
@@ -3049,7 +2315,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -3329,104 +2595,104 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="9" t="n">
+      <c r="A54" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="9" t="inlineStr"/>
-      <c r="C54" s="9" t="inlineStr">
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
         <is>
           <t>vo_p7_h1</t>
         </is>
       </c>
-      <c r="D54" s="9" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>vo_p7_h1.wav</t>
         </is>
       </c>
-      <c r="E54" s="10" t="inlineStr">
+      <c r="E54" s="8" t="inlineStr">
         <is>
           <t>फिर से सुनिए। जिन शब्दों की शुरुआत ‘च’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="F54" s="9" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>page 9 · h1</t>
         </is>
       </c>
-      <c r="G54" s="9" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-      <c r="H54" s="9" t="n">
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
         <v>76</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="n">
+      <c r="A55" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="9" t="inlineStr"/>
-      <c r="C55" s="9" t="inlineStr">
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
         <is>
           <t>vo_p7_h2</t>
         </is>
       </c>
-      <c r="D55" s="9" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>vo_p7_h2.wav</t>
         </is>
       </c>
-      <c r="E55" s="10" t="inlineStr">
+      <c r="E55" s="8" t="inlineStr">
         <is>
           <t>जिन शब्दों की शुरुआत ‘च’ की आवाज़ से होती है, उन पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="F55" s="9" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>page 9 · h2</t>
         </is>
       </c>
-      <c r="G55" s="9" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-      <c r="H55" s="9" t="n">
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
         <v>62</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="9" t="n">
+      <c r="A56" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="9" t="inlineStr"/>
-      <c r="C56" s="9" t="inlineStr">
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
         <is>
           <t>vo_p7_h3</t>
         </is>
       </c>
-      <c r="D56" s="9" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>vo_p7_h3.wav</t>
         </is>
       </c>
-      <c r="E56" s="10" t="inlineStr">
+      <c r="E56" s="8" t="inlineStr">
         <is>
           <t>देखिए, ‘चाँद’ और ‘चश्मा’ की शुरुआत ‘च’ की आवाज़ से होती है। इन पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="F56" s="9" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>page 9 · h3</t>
         </is>
       </c>
-      <c r="G56" s="9" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-      <c r="H56" s="9" t="n">
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
         <v>76</v>
       </c>
     </row>
@@ -3673,70 +2939,70 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="9" t="n">
+      <c r="A64" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="9" t="inlineStr"/>
-      <c r="C64" s="9" t="inlineStr">
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
         <is>
           <t>vo_g3_h1</t>
         </is>
       </c>
-      <c r="D64" s="9" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>vo_g3_h1.wav</t>
         </is>
       </c>
-      <c r="E64" s="10" t="inlineStr">
+      <c r="E64" s="8" t="inlineStr">
         <is>
           <t>फिर से पढ़िए।</t>
         </is>
       </c>
-      <c r="F64" s="9" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>page 10 · h1</t>
         </is>
       </c>
-      <c r="G64" s="9" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-      <c r="H64" s="9" t="n">
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="9" t="n">
+      <c r="A65" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="9" t="inlineStr"/>
-      <c r="C65" s="9" t="inlineStr">
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
         <is>
           <t>vo_g3_h3</t>
         </is>
       </c>
-      <c r="D65" s="9" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>vo_g3_h3.wav</t>
         </is>
       </c>
-      <c r="E65" s="10" t="inlineStr">
+      <c r="E65" s="8" t="inlineStr">
         <is>
           <t>चूहे, चार, चने, चबाए… इन सबमें ‘च’ की आवाज़ है। ‘च’ पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="F65" s="9" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>page 10 · h3</t>
         </is>
       </c>
-      <c r="G65" s="9" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-      <c r="H65" s="9" t="n">
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
         <v>65</v>
       </c>
     </row>
@@ -3915,70 +3181,70 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="9" t="n">
+      <c r="A71" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="9" t="inlineStr"/>
-      <c r="C71" s="9" t="inlineStr">
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
         <is>
           <t>vo_p4_h1</t>
         </is>
       </c>
-      <c r="D71" s="9" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>vo_p4_h1.wav</t>
         </is>
       </c>
-      <c r="E71" s="10" t="inlineStr">
+      <c r="E71" s="8" t="inlineStr">
         <is>
           <t>फिर से पढ़िए।</t>
         </is>
       </c>
-      <c r="F71" s="9" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>page 11 · h1</t>
         </is>
       </c>
-      <c r="G71" s="9" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-      <c r="H71" s="9" t="n">
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="9" t="n">
+      <c r="A72" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="9" t="inlineStr"/>
-      <c r="C72" s="9" t="inlineStr">
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
         <is>
           <t>vo_p4_h3</t>
         </is>
       </c>
-      <c r="D72" s="9" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>vo_p4_h3.wav</t>
         </is>
       </c>
-      <c r="E72" s="10" t="inlineStr">
+      <c r="E72" s="8" t="inlineStr">
         <is>
           <t>नानी, ने, नई, नाव… इन सबकी शुरुआत ‘न’ की आवाज़ से होती है। ‘न’ पर टैप कीजिए।</t>
         </is>
       </c>
-      <c r="F72" s="9" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>page 11 · h3</t>
         </is>
       </c>
-      <c r="G72" s="9" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-      <c r="H72" s="9" t="n">
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
         <v>76</v>
       </c>
     </row>
@@ -4123,36 +3389,36 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="9" t="n">
+      <c r="A77" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="9" t="inlineStr"/>
-      <c r="C77" s="9" t="inlineStr">
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr">
         <is>
           <t>vo_g5_h1</t>
         </is>
       </c>
-      <c r="D77" s="9" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>vo_g5_h1.wav</t>
         </is>
       </c>
-      <c r="E77" s="10" t="inlineStr">
+      <c r="E77" s="8" t="inlineStr">
         <is>
           <t>फिर से सुनिए। चित्र का नाम ध्यान से सुनिए और देखिए उसकी शुरुआत किस आवाज़ से होती है।</t>
         </is>
       </c>
-      <c r="F77" s="9" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>page 12 · h1 (2nd half)</t>
         </is>
       </c>
-      <c r="G77" s="9" t="inlineStr">
-        <is>
-          <t>NOT RECORDED - new line, needs a first take</t>
-        </is>
-      </c>
-      <c r="H77" s="9" t="n">
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>delivered - do NOT re-record</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
         <v>84</v>
       </c>
     </row>
@@ -4459,7 +3725,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="H86" t="n">
@@ -4691,7 +3957,7 @@
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>शाबाश! आज हमने सीखा — वाक्य ध्यान से सुनना, बार-बार आने वाली आवाज़ पहचानना, और प, च और म की आवाज़ ढूँढना।</t>
+          <t>बहुत बढ़िया, दोस्त! तुमने कमाल कर दिया!</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4701,11 +3967,11 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>RE-RECORD - build differs from the delivered take</t>
+          <t>delivered - do NOT re-record</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>105</v>
+        <v>39</v>
       </c>
     </row>
     <row r="94">
